--- a/project_2/project2_project status(C2)xlsx.xlsx
+++ b/project_2/project2_project status(C2)xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA281C9A-F170-4272-9F94-7F51A34E59D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2028125F-BBE8-410F-A8D7-4BF23F86D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -34,15 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="196">
   <si>
     <t>reward</t>
   </si>
   <si>
     <t>channels</t>
-  </si>
-  <si>
-    <t>difficulty</t>
   </si>
   <si>
     <t>duration</t>
@@ -286,9 +283,6 @@
     <t>각 가지는 검증 가능한 형태로 작성한다: “~하면 ~할 것이다”</t>
   </si>
   <si>
-    <t>MECE 여부를 팀 내에서 상호 검토한다.</t>
-  </si>
-  <si>
     <r>
       <t>산출물</t>
     </r>
@@ -345,9 +339,6 @@
   </si>
   <si>
     <t>확인할 점</t>
-  </si>
-  <si>
-    <t>각 가지가 참·거짓을 판정할 수 있는 명제로 서술되어 있다.</t>
   </si>
   <si>
     <t>아직 데이터를 보지 않았으므로 어느 가지가 맞는지 모르는 상태다.</t>
@@ -918,15 +909,44 @@
     <t>발표</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>문제 정의</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>배경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer(행사) 설계에 따라 주문 완료율의 차이가 있는가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스타벅스는 bogo(1+1), discount(할인), informational(정보성) 3가지 유형의 행사를 운영하고 있으며, 각 오퍼마다 보상액(reward)이 다르게 책정되어 있음.
+어떤 설계 요소가 고객의 완료율에 실제로 영향을 미치는지 파악하면, 향후 오퍼 설계를 데이터 기반으로 최적화할 수 있음.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MECE 여부를 팀 내에서 상호 검토한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficulty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 가지가 참·거짓을 판정할 수 있는 명제로 서술되어 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="182" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,6 +1028,23 @@
       <name val="Arial Unicode MS"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1241,7 +1278,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1295,33 +1332,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1380,8 +1390,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1398,6 +1444,6356 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/diagrams/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:colorsDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/colors/accent6_2">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="accent6" pri="11200"/>
+  </dgm:catLst>
+  <dgm:styleLbl name="node0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="dk1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+</dgm:colorsDef>
+</file>
+
+<file path=xl/diagrams/data1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:dataModel xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dgm:ptLst>
+    <dgm:pt modelId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" type="doc">
+      <dgm:prSet loTypeId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2" loCatId="hierarchy" qsTypeId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1" qsCatId="simple" csTypeId="urn:microsoft.com/office/officeart/2005/8/colors/accent6_2" csCatId="accent6" phldr="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1">
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>행사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8FA42352-D834-44A6-A154-3CB76BE81B68}" type="parTrans" cxnId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{71F878CA-1A36-404F-978F-D8724DEDCCAF}" type="sibTrans" cxnId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer type</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" type="parTrans" cxnId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{33CA151E-3B69-4314-B123-3297DFC7D670}" type="sibTrans" cxnId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" type="parTrans" cxnId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{E023194C-F95D-4763-92F5-F1ECD4BC9C73}" type="sibTrans" cxnId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(4.2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" type="parTrans" cxnId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B9BFC1E1-36FA-4DFA-A7FB-937425619DD8}" type="sibTrans" cxnId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>완료율은 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>discount &gt; bogo &gt; information </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>순으로 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B0E34315-446D-43CA-9C1A-43AC03C7FA4E}" type="sibTrans" cxnId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" type="parTrans" cxnId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>기간</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" type="parTrans" cxnId="{C5516619-C5B2-4288-84CD-67C055A97476}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{05412BF9-284B-4F1C-86AC-AF524BDD7D14}" type="sibTrans" cxnId="{C5516619-C5B2-4288-84CD-67C055A97476}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(6.7)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" type="parTrans" cxnId="{F7115254-B2DB-4711-9B96-1797D64046C8}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{827A2A25-BF22-45D1-8C10-6D340F70C6A1}" type="sibTrans" cxnId="{F7115254-B2DB-4711-9B96-1797D64046C8}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3E881757-362F-489E-B630-0D8A32984B2B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Channels</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" type="parTrans" cxnId="{8CEC1554-B055-464F-AC47-FCFB34B80966}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{278E719C-4D84-4910-9C25-3DCD78815614}" type="sibTrans" cxnId="{8CEC1554-B055-464F-AC47-FCFB34B80966}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" type="parTrans" cxnId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{213EC674-33B2-46B5-97B4-B78DD7CC6633}" type="sibTrans" cxnId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" type="parTrans" cxnId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{DE75E50D-DFA6-418B-9C06-95A5C3944847}" type="sibTrans" cxnId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Social</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" type="parTrans" cxnId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{81FA6521-2044-4D8B-A3F2-96C820EAF9F1}" type="sibTrans" cxnId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>email</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" type="parTrans" cxnId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D56ED9E6-07E6-476D-B72A-1DAC45654595}" type="sibTrans" cxnId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" type="parTrans" cxnId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B5F3BFB9-0C8D-4ED3-BB39-6E65AD6E6202}" type="sibTrans" cxnId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{F145AA98-6443-4870-A7B4-EC590B09FF29}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(7.7) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{61B28454-54A2-4A23-B946-6072BC34D484}" type="parTrans" cxnId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{F87A8A7F-0D3D-4479-81E7-4B421A7751B7}" type="sibTrans" cxnId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" type="pres">
+      <dgm:prSet presAssocID="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" presName="diagram" presStyleCnt="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="1"/>
+          <dgm:dir/>
+          <dgm:animOne val="branch"/>
+          <dgm:animLvl val="lvl"/>
+          <dgm:resizeHandles val="exact"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="root1" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="1" custScaleX="156668">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="level2hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}" type="pres">
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" type="pres">
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{01253263-E07D-4F9F-8798-5E3E260C947E}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="5">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" type="pres">
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" type="pres">
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="8" custScaleX="313336" custLinFactNeighborX="-620">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{43A0655B-ED0B-4D66-84EA-7B531B0D95AE}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" type="pres">
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" type="pres">
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="5">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" type="pres">
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" type="pres">
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F3AD275D-DDC7-48F0-8A1B-913C9D7C169E}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}" type="pres">
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" type="pres">
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="5">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" type="pres">
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" type="pres">
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{86B928B2-71C3-47DC-B28B-9D75DAEBBA8C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}" type="pres">
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" type="pres">
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F3B7EAB8-F828-469D-957A-9C0140751550}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="5">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" type="pres">
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" type="pres">
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{7DB0F5C2-B6D7-40CB-93B1-A32531C856A9}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}" type="pres">
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" type="pres">
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{2D542640-C237-42B5-8470-73084719F8F3}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A57B83BB-BCC1-45F0-B448-0696169F3FCC}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" type="pres">
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" type="pres">
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{38EBA6BB-7DEA-4839-B386-BF85BFBB7A06}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" type="pres">
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" type="pres">
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{220D319D-36C0-42A0-A946-F197C4269C14}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{5AC15471-6EAA-4265-8E4D-6043A7CECF67}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4332858F-88A7-466E-8722-8833A7B96598}" type="pres">
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" type="pres">
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="5"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{41714DC3-F3A7-41BB-8371-656B34451539}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="5">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{5B364536-61C6-4C87-983E-3D7708A352A0}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" type="pres">
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{274B025F-D16B-4968-87D0-380BD22343AE}" type="pres">
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="8" custScaleX="313336">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{98E7E4BB-43E7-4635-B1B5-7AAB6FB148D9}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+  </dgm:ptLst>
+  <dgm:cxnLst>
+    <dgm:cxn modelId="{E716BF02-E552-4CCD-89CD-A5B0B6E9EC70}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" srcOrd="1" destOrd="0" parTransId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" sibTransId="{D56ED9E6-07E6-476D-B72A-1DAC45654595}"/>
+    <dgm:cxn modelId="{AF850C0E-477F-45E3-A0A3-1F4786C24FFD}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{274B025F-D16B-4968-87D0-380BD22343AE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6789530F-FB45-46BA-9B1D-3B3341D4D748}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{ED5992BD-91A0-44DC-B026-C230E027754F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D62D4711-4853-49C5-AD88-6A4C204E26FD}" type="presOf" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E147F012-F227-46EA-B01A-D20475D3B67D}" type="presOf" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" srcOrd="0" destOrd="0" parTransId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" sibTransId="{33CA151E-3B69-4314-B123-3297DFC7D670}"/>
+    <dgm:cxn modelId="{C5516619-C5B2-4288-84CD-67C055A97476}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" srcOrd="2" destOrd="0" parTransId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" sibTransId="{05412BF9-284B-4F1C-86AC-AF524BDD7D14}"/>
+    <dgm:cxn modelId="{814B5B2D-0636-46D6-8357-3E465A736B44}" type="presOf" srcId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" destId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{598EE134-21B8-4BC4-B868-2937D8E35E75}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{806C8330-1E37-41AD-AEEE-3552A4162510}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{11932F3D-BA9B-441A-8939-E3C049AD81D3}" type="presOf" srcId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" destId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{649BBD44-4CFF-49CE-B5C2-02F87A124FCF}" type="presOf" srcId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" destId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{719F1E48-19AF-416D-BC2E-82961DFA1755}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D92FE84D-8344-484F-96C7-CD04C772FFCE}" type="presOf" srcId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" srcOrd="2" destOrd="0" parTransId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" sibTransId="{DE75E50D-DFA6-418B-9C06-95A5C3944847}"/>
+    <dgm:cxn modelId="{8CEC1554-B055-464F-AC47-FCFB34B80966}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{3E881757-362F-489E-B630-0D8A32984B2B}" srcOrd="3" destOrd="0" parTransId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" sibTransId="{278E719C-4D84-4910-9C25-3DCD78815614}"/>
+    <dgm:cxn modelId="{F7115254-B2DB-4711-9B96-1797D64046C8}" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" srcOrd="0" destOrd="0" parTransId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" sibTransId="{827A2A25-BF22-45D1-8C10-6D340F70C6A1}"/>
+    <dgm:cxn modelId="{CAEBC875-3C11-4DF4-B17E-40CDB162EBA4}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" srcOrd="1" destOrd="0" parTransId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" sibTransId="{E023194C-F95D-4763-92F5-F1ECD4BC9C73}"/>
+    <dgm:cxn modelId="{D2FA5A79-1C6F-4BA4-9743-73F806A7B41B}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" srcOrd="0" destOrd="0" parTransId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" sibTransId="{213EC674-33B2-46B5-97B4-B78DD7CC6633}"/>
+    <dgm:cxn modelId="{9E93E484-6F94-455F-905B-83CCF7FF2B2F}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BE014B86-3D98-439A-9866-D73914E0EE7E}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{604F8188-5220-4BBD-B051-AE258F4786C5}" type="presOf" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9554478A-1EB0-4AAA-ADAE-9FB3873C43EB}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8462148B-1DD3-441F-B63F-6F0F33CA55E6}" type="presOf" srcId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" destId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{AB24B48B-7C7E-4598-9A0B-41A35655D90D}" type="presOf" srcId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" destId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{00C77A8E-6B70-42A2-9561-C73F86BE4CF8}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CF369B92-780C-46D0-9ED6-7B81FBADD727}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{17E63997-D9CE-4D39-AE2E-A3AE0D1284BC}" type="presOf" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" srcOrd="0" destOrd="0" parTransId="{61B28454-54A2-4A23-B946-6072BC34D484}" sibTransId="{F87A8A7F-0D3D-4479-81E7-4B421A7751B7}"/>
+    <dgm:cxn modelId="{24D5F7A1-BC55-49BA-AD3A-9E7950427D56}" type="presOf" srcId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" destId="{2D542640-C237-42B5-8470-73084719F8F3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" srcOrd="0" destOrd="0" parTransId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" sibTransId="{B0E34315-446D-43CA-9C1A-43AC03C7FA4E}"/>
+    <dgm:cxn modelId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" srcOrd="0" destOrd="0" parTransId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" sibTransId="{B9BFC1E1-36FA-4DFA-A7FB-937425619DD8}"/>
+    <dgm:cxn modelId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" srcOrd="0" destOrd="0" parTransId="{8FA42352-D834-44A6-A154-3CB76BE81B68}" sibTransId="{71F878CA-1A36-404F-978F-D8724DEDCCAF}"/>
+    <dgm:cxn modelId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" srcOrd="4" destOrd="0" parTransId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" sibTransId="{B5F3BFB9-0C8D-4ED3-BB39-6E65AD6E6202}"/>
+    <dgm:cxn modelId="{A37199AF-6B7B-4D63-9BED-72A4088E31D7}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{356B8AB4-45AE-46AE-8283-651F355AD458}" type="presOf" srcId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" destId="{16F44D37-2601-482A-9095-0B3E8E10E520}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9E72F2B5-B38B-4682-A94E-6A0A12C507BD}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C2E5C8C2-39E3-4172-B04E-F41ADFDEB387}" type="presOf" srcId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" destId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{FB2B60CC-0744-4CF3-81D8-7AD4A3610137}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{227E0FEF-1368-4562-AD55-940C6A450E91}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A20F76D0-7BCB-45E8-B360-790EB5F29686}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DBF535D2-BD92-4672-8867-EA84BC5763AA}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2440BBD3-B375-44FF-872D-AB1B780F978C}" type="presOf" srcId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" destId="{106C3051-36E0-4DB2-B006-BD51244834C6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" srcOrd="3" destOrd="0" parTransId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" sibTransId="{81FA6521-2044-4D8B-A3F2-96C820EAF9F1}"/>
+    <dgm:cxn modelId="{22675FDB-D57E-40A9-8DB8-24BDE2145037}" type="presOf" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D9CA61DC-2D30-46B4-A093-77D4B2F30BE9}" type="presOf" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{146FB508-948A-484E-B54F-2A63CE5492FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4FE23EDF-13FE-4703-91E6-6C903EDF68FE}" type="presOf" srcId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" destId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3D57FDE0-4E64-475C-A9CE-314E2DD7D40C}" type="presOf" srcId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" destId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CCFD01E6-B250-4974-8ACC-B4488D55724F}" type="presOf" srcId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" destId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6AA869F1-2370-47CB-8892-04E1C8E66198}" type="presOf" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D46966F4-1F6B-44AE-BBA7-9D94EA384573}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{4332858F-88A7-466E-8722-8833A7B96598}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6BB77CF6-5C09-47BD-BAE8-C3CAB397D44B}" type="presOf" srcId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" destId="{220D319D-36C0-42A0-A946-F197C4269C14}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B2374AFC-17E8-4D47-98A5-8F67B836CE42}" type="presOf" srcId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" destId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D031EAFE-71D3-4118-AE8A-0807172E90A8}" type="presOf" srcId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" destId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F0990498-35A7-462E-866E-ACEAAF852A57}" type="presParOf" srcId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" destId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3AC408DF-32EB-43BA-8E9D-8489B358660D}" type="presParOf" srcId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" destId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92D88567-4A9F-42AA-9F6E-33826FCBD533}" type="presParOf" srcId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" destId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1ACA0D17-5E35-4CFA-8079-DAFD961015B2}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{ED5992BD-91A0-44DC-B026-C230E027754F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{33117CAB-5F87-46A4-A41A-86AADB73DD34}" type="presParOf" srcId="{ED5992BD-91A0-44DC-B026-C230E027754F}" destId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2AED2644-195B-416B-931E-6BB1466C1C4A}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{01253263-E07D-4F9F-8798-5E3E260C947E}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3EF7D83A-D253-4220-A811-2E9019FF47D7}" type="presParOf" srcId="{01253263-E07D-4F9F-8798-5E3E260C947E}" destId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9280AB69-4EA9-4E66-B6D0-D9ED1CDBC799}" type="presParOf" srcId="{01253263-E07D-4F9F-8798-5E3E260C947E}" destId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C42022F0-ECCE-427A-A81C-AC7B4EAEC80C}" type="presParOf" srcId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" destId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{189FEFF2-4AB3-49B1-97F5-0ECB96BF88AB}" type="presParOf" srcId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" destId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8D0AEE37-7FF5-418B-92BC-1C2FAFBF000D}" type="presParOf" srcId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" destId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D8BB15FE-DCFF-4753-8F06-32BC8629183E}" type="presParOf" srcId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" destId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B6461975-0FB2-4AAB-893C-FAD81A2D7269}" type="presParOf" srcId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" destId="{43A0655B-ED0B-4D66-84EA-7B531B0D95AE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{ECEA538B-A558-48F6-9110-1111D6DD0D77}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9F778866-158D-4384-BC59-E9DB8C750120}" type="presParOf" srcId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" destId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{14D89E3F-57C4-4140-AD2C-B4ADEAE79FE3}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BCE7A905-25BB-4121-99D9-E77A96DB44B6}" type="presParOf" srcId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" destId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DB7E9FA7-536B-492C-B2B1-E11F697A4743}" type="presParOf" srcId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" destId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9F52891E-146C-47EE-842A-744C883BBAB2}" type="presParOf" srcId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" destId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4F1172A1-42ED-42CF-8ACD-E60DE8D12795}" type="presParOf" srcId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" destId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8948BCFA-B8A4-4C32-BD1A-2F380A04ECB3}" type="presParOf" srcId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" destId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A98A6079-322E-4202-83F6-91B20AC9541D}" type="presParOf" srcId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" destId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6EA2B04B-A1F1-41D4-9B62-39CBB7A5A316}" type="presParOf" srcId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" destId="{F3AD275D-DDC7-48F0-8A1B-913C9D7C169E}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{67910EB1-0A61-4384-B152-314479FD6F36}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{806C8330-1E37-41AD-AEEE-3552A4162510}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BACC5A24-2505-418E-9A53-CF08A484382E}" type="presParOf" srcId="{806C8330-1E37-41AD-AEEE-3552A4162510}" destId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1D75447D-C931-4C31-8481-7E0BD53DB138}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6168A3CE-8F8B-4DC5-92F8-C2896537B2D6}" type="presParOf" srcId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" destId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B7B0153F-08CE-45FF-B381-232B8FCFC287}" type="presParOf" srcId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" destId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{528009D1-C30F-4548-86DF-51860FC776EE}" type="presParOf" srcId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" destId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C3B293A9-4878-4E4F-9881-FD4F72AA8476}" type="presParOf" srcId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" destId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{27042C1C-D24D-4B77-8B9A-FE733F7AFAC0}" type="presParOf" srcId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" destId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A3A73319-F2D0-4533-9A6A-EBA21A7D2F2B}" type="presParOf" srcId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" destId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F8FB85BE-7E42-4355-A81C-5F83980F9040}" type="presParOf" srcId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" destId="{86B928B2-71C3-47DC-B28B-9D75DAEBBA8C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{443338C9-C8A9-414F-BCCE-48D2877357F4}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{227E0FEF-1368-4562-AD55-940C6A450E91}" srcOrd="6" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92250F63-1AAE-49DA-83B9-37528C221006}" type="presParOf" srcId="{227E0FEF-1368-4562-AD55-940C6A450E91}" destId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8E464938-4467-422D-B278-93028012F661}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{F3B7EAB8-F828-469D-957A-9C0140751550}" srcOrd="7" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F1FD993C-3C4A-4702-BD6B-E3BBBCF9E2AA}" type="presParOf" srcId="{F3B7EAB8-F828-469D-957A-9C0140751550}" destId="{146FB508-948A-484E-B54F-2A63CE5492FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{060D572C-F523-4B2E-A330-612D5B7CFE19}" type="presParOf" srcId="{F3B7EAB8-F828-469D-957A-9C0140751550}" destId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2156532E-A97E-45AB-AD43-90A1314BCE00}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{22E15C8A-4485-47DF-AF00-2D8C68D9CE28}" type="presParOf" srcId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" destId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92CD3A7C-823F-4FFF-8F29-111AE5C0461E}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D28625AC-D7D2-4704-935E-542DCA4A7B7C}" type="presParOf" srcId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" destId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D47EBECA-8B8B-495C-AFFB-FF1D4A03325B}" type="presParOf" srcId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" destId="{7DB0F5C2-B6D7-40CB-93B1-A32531C856A9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CC9583AB-705F-4AC4-92C7-60FD3AD62A33}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{16F44D37-2601-482A-9095-0B3E8E10E520}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{04AC06F6-1BA3-423E-9904-D1A1315EF5EB}" type="presParOf" srcId="{16F44D37-2601-482A-9095-0B3E8E10E520}" destId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{13E0708D-FB2F-4B73-93F5-45C8C5101766}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9FA603F9-A823-4748-86E6-F01C9E6B1CA2}" type="presParOf" srcId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" destId="{2D542640-C237-42B5-8470-73084719F8F3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7D7D6007-1FF7-4FFF-8DD8-0CD84FA4770D}" type="presParOf" srcId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" destId="{A57B83BB-BCC1-45F0-B448-0696169F3FCC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3C2082E4-769F-4B64-B7B4-251DF5B7D113}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3F42D1BF-67A9-4068-BE00-438C7BE5AF65}" type="presParOf" srcId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" destId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DA2D3530-1BAD-497A-803D-83550958E960}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F353278E-3CF5-4A11-879B-038B8BFEF605}" type="presParOf" srcId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" destId="{106C3051-36E0-4DB2-B006-BD51244834C6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BAA1BA9A-727F-4416-BB25-2958C87CE731}" type="presParOf" srcId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" destId="{38EBA6BB-7DEA-4839-B386-BF85BFBB7A06}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{11D03BA6-E3B1-4ECB-A910-EC30A0DA4471}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" srcOrd="6" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E6498285-E404-4729-A740-16A0B3118A32}" type="presParOf" srcId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" destId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BD9B2FA7-2273-40BB-9248-46BD8C95A622}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" srcOrd="7" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7326FC10-C75F-44B4-911D-EE10AE932C2D}" type="presParOf" srcId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" destId="{220D319D-36C0-42A0-A946-F197C4269C14}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D8D362A0-9FE8-45B5-AA5D-067962F1F7B4}" type="presParOf" srcId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" destId="{5AC15471-6EAA-4265-8E4D-6043A7CECF67}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E5BEC14D-A9A1-4355-A3A9-1E377AA2AC54}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{4332858F-88A7-466E-8722-8833A7B96598}" srcOrd="8" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E6163E19-FB3F-4C0B-98E5-A3B8DC0CC4B4}" type="presParOf" srcId="{4332858F-88A7-466E-8722-8833A7B96598}" destId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6D16ED87-2BB7-463C-A03E-FBBA687DE88B}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{41714DC3-F3A7-41BB-8371-656B34451539}" srcOrd="9" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5323B34C-18BF-44DD-A72B-7534F485E8E6}" type="presParOf" srcId="{41714DC3-F3A7-41BB-8371-656B34451539}" destId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A4474184-E87A-47CA-A300-E601A3C5A774}" type="presParOf" srcId="{41714DC3-F3A7-41BB-8371-656B34451539}" destId="{5B364536-61C6-4C87-983E-3D7708A352A0}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A50E6F8F-098B-4D29-A5F8-4055DAC56E62}" type="presParOf" srcId="{5B364536-61C6-4C87-983E-3D7708A352A0}" destId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{984B8066-3C74-429A-8267-038C32534B0D}" type="presParOf" srcId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" destId="{274B025F-D16B-4968-87D0-380BD22343AE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E595B179-46DA-4256-9CC9-35B70B57CAE1}" type="presParOf" srcId="{5B364536-61C6-4C87-983E-3D7708A352A0}" destId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BAEA4C6F-55B1-4D11-A93D-613622995B8E}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E7A12BF5-6203-42EB-8DFF-6FE7ABF53C31}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{98E7E4BB-43E7-4635-B1B5-7AAB6FB148D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+  </dgm:cxnLst>
+  <dgm:bg>
+    <a:solidFill>
+      <a:schemeClr val="accent4">
+        <a:lumMod val="20000"/>
+        <a:lumOff val="80000"/>
+      </a:schemeClr>
+    </a:solidFill>
+  </dgm:bg>
+  <dgm:whole/>
+  <dgm:extLst>
+    <a:ext uri="http://schemas.microsoft.com/office/drawing/2008/diagram">
+      <dsp:dataModelExt xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" relId="rId5" minVer="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+    </a:ext>
+    <a:ext uri="{C62137D5-CB1D-491B-B009-E17868A290BF}">
+      <dgm14:recolorImg xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" val="1"/>
+    </a:ext>
+  </dgm:extLst>
+</dgm:dataModel>
+</file>
+
+<file path=xl/diagrams/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<dsp:drawing xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dsp:spTree>
+    <dsp:nvGrpSpPr>
+      <dsp:cNvPr id="0" name=""/>
+      <dsp:cNvGrpSpPr/>
+    </dsp:nvGrpSpPr>
+    <dsp:grpSpPr/>
+    <dsp:sp modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="244948" y="1988314"/>
+          <a:ext cx="1545781" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>행사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="259397" y="2002763"/>
+        <a:ext cx="1516883" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="16874489">
+          <a:off x="975814" y="1232219"/>
+          <a:ext cx="2024496" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="2024496" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1937449" y="1191539"/>
+        <a:ext cx="101224" cy="101224"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2185394" y="2659"/>
+          <a:ext cx="986660" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer type</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2199843" y="17108"/>
+        <a:ext cx="957762" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3172055" y="239391"/>
+          <a:ext cx="388547" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="388547" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3356615" y="239611"/>
+        <a:ext cx="19427" cy="19427"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3560602" y="2659"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>완료율은 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>discount &gt; bogo &gt; information </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>순으로 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3575051" y="17108"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17132988">
+          <a:off x="1251956" y="1515884"/>
+          <a:ext cx="1472211" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="1472211" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1951257" y="1489012"/>
+        <a:ext cx="73610" cy="73610"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2185394" y="569989"/>
+          <a:ext cx="986660" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2199843" y="584438"/>
+        <a:ext cx="957762" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3172055" y="806721"/>
+          <a:ext cx="394664" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="394664" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3359521" y="806788"/>
+        <a:ext cx="19733" cy="19733"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="569989"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(4.2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="584438"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17692822">
+          <a:off x="1519033" y="1799549"/>
+          <a:ext cx="938057" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="938057" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1964610" y="1786031"/>
+        <a:ext cx="46902" cy="46902"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2185394" y="1137319"/>
+          <a:ext cx="986660" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>기간</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2199843" y="1151768"/>
+        <a:ext cx="957762" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3172055" y="1374052"/>
+          <a:ext cx="394664" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="394664" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3359521" y="1374118"/>
+        <a:ext cx="19733" cy="19733"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="1137319"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(6.7)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="1151768"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="3310531">
+          <a:off x="1642510" y="2508712"/>
+          <a:ext cx="691103" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="691103" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1970784" y="2501367"/>
+        <a:ext cx="34555" cy="34555"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2185394" y="2555644"/>
+          <a:ext cx="986660" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Channels</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2199843" y="2570093"/>
+        <a:ext cx="957762" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17692822">
+          <a:off x="2900358" y="2366879"/>
+          <a:ext cx="938057" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="938057" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3345936" y="2353361"/>
+        <a:ext cx="46902" cy="46902"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="1704649"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="1719098"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="19457599">
+          <a:off x="3126372" y="2650544"/>
+          <a:ext cx="486030" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="486030" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3357236" y="2648326"/>
+        <a:ext cx="24301" cy="24301"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="2271979"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>email</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="2286428"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="2142401">
+          <a:off x="3126372" y="2934209"/>
+          <a:ext cx="486030" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="486030" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3357236" y="2931991"/>
+        <a:ext cx="24301" cy="24301"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="2839309"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="2853758"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="3907178">
+          <a:off x="2900358" y="3217874"/>
+          <a:ext cx="938057" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="938057" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3345936" y="3204356"/>
+        <a:ext cx="46902" cy="46902"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="3406639"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Social</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="3421088"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="4725511">
+          <a:off x="975814" y="3217874"/>
+          <a:ext cx="2024496" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="2024496" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1937449" y="3177195"/>
+        <a:ext cx="101224" cy="101224"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2185394" y="3973969"/>
+          <a:ext cx="986660" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2199843" y="3988418"/>
+        <a:ext cx="957762" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3172055" y="4210702"/>
+          <a:ext cx="394664" cy="19865"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="9932"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="394664" y="9932"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3359521" y="4210768"/>
+        <a:ext cx="19733" cy="19733"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3566719" y="3973969"/>
+          <a:ext cx="3091563" cy="493330"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(7.7) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3581168" y="3988418"/>
+        <a:ext cx="3062665" cy="464432"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+  </dsp:spTree>
+</dsp:drawing>
+</file>
+
+<file path=xl/diagrams/layout1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:layoutDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="hierarchy" pri="5000"/>
+  </dgm:catLst>
+  <dgm:sampData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="2">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="21">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="22">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="3">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="31">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="4" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="5" srcId="1" destId="2" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="6" srcId="1" destId="3" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="23" srcId="2" destId="21" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="24" srcId="2" destId="22" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="33" srcId="3" destId="31" srcOrd="0" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:sampData>
+  <dgm:styleData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="11"/>
+        <dgm:pt modelId="12"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="2" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="13" srcId="1" destId="11" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="14" srcId="1" destId="12" srcOrd="1" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:styleData>
+  <dgm:clrData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="2"/>
+        <dgm:pt modelId="21"/>
+        <dgm:pt modelId="211"/>
+        <dgm:pt modelId="3"/>
+        <dgm:pt modelId="31"/>
+        <dgm:pt modelId="311"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="4" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="5" srcId="1" destId="2" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="6" srcId="1" destId="3" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="23" srcId="2" destId="21" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="24" srcId="21" destId="211" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="33" srcId="3" destId="31" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="34" srcId="31" destId="311" srcOrd="0" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:clrData>
+  <dgm:layoutNode name="diagram">
+    <dgm:varLst>
+      <dgm:chPref val="1"/>
+      <dgm:dir/>
+      <dgm:animOne val="branch"/>
+      <dgm:animLvl val="lvl"/>
+      <dgm:resizeHandles val="exact"/>
+    </dgm:varLst>
+    <dgm:choose name="Name0">
+      <dgm:if name="Name1" func="var" arg="dir" op="equ" val="norm">
+        <dgm:alg type="hierChild">
+          <dgm:param type="linDir" val="fromT"/>
+          <dgm:param type="chAlign" val="l"/>
+        </dgm:alg>
+      </dgm:if>
+      <dgm:else name="Name2">
+        <dgm:alg type="hierChild">
+          <dgm:param type="linDir" val="fromT"/>
+          <dgm:param type="chAlign" val="r"/>
+        </dgm:alg>
+      </dgm:else>
+    </dgm:choose>
+    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+      <dgm:adjLst/>
+    </dgm:shape>
+    <dgm:presOf/>
+    <dgm:constrLst>
+      <dgm:constr type="h" for="des" ptType="node" refType="h"/>
+      <dgm:constr type="w" for="des" ptType="node" refType="h" refFor="des" refPtType="node" fact="2"/>
+      <dgm:constr type="sibSp" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sibSp" for="des" forName="level2hierChild" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sibSp" for="des" forName="level3hierChild" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sp" for="des" forName="root1" refType="w" refFor="des" refPtType="node" fact="0.4"/>
+      <dgm:constr type="sp" for="des" forName="root2" refType="sp" refFor="des" refForName="root1" op="equ"/>
+      <dgm:constr type="primFontSz" for="des" ptType="node" op="equ" val="65"/>
+      <dgm:constr type="primFontSz" for="des" forName="connTx" op="equ" val="55"/>
+      <dgm:constr type="primFontSz" for="des" forName="connTx" refType="primFontSz" refFor="des" refPtType="node" op="lte" fact="0.8"/>
+    </dgm:constrLst>
+    <dgm:ruleLst/>
+    <dgm:forEach name="Name3" axis="ch">
+      <dgm:forEach name="Name4" axis="self" ptType="node">
+        <dgm:layoutNode name="root1">
+          <dgm:choose name="Name5">
+            <dgm:if name="Name6" func="var" arg="dir" op="equ" val="norm">
+              <dgm:alg type="hierRoot">
+                <dgm:param type="hierAlign" val="lCtrCh"/>
+              </dgm:alg>
+            </dgm:if>
+            <dgm:else name="Name7">
+              <dgm:alg type="hierRoot">
+                <dgm:param type="hierAlign" val="rCtrCh"/>
+              </dgm:alg>
+            </dgm:else>
+          </dgm:choose>
+          <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+            <dgm:adjLst/>
+          </dgm:shape>
+          <dgm:presOf/>
+          <dgm:constrLst/>
+          <dgm:ruleLst/>
+          <dgm:layoutNode name="LevelOneTextNode" styleLbl="node0">
+            <dgm:varLst>
+              <dgm:chPref val="3"/>
+            </dgm:varLst>
+            <dgm:alg type="tx"/>
+            <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="roundRect" r:blip="">
+              <dgm:adjLst>
+                <dgm:adj idx="1" val="0.1"/>
+              </dgm:adjLst>
+            </dgm:shape>
+            <dgm:presOf axis="self"/>
+            <dgm:constrLst>
+              <dgm:constr type="tMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="bMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="lMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="rMarg" refType="primFontSz" fact="0.05"/>
+            </dgm:constrLst>
+            <dgm:ruleLst>
+              <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+            </dgm:ruleLst>
+          </dgm:layoutNode>
+          <dgm:layoutNode name="level2hierChild">
+            <dgm:choose name="Name8">
+              <dgm:if name="Name9" func="var" arg="dir" op="equ" val="norm">
+                <dgm:alg type="hierChild">
+                  <dgm:param type="linDir" val="fromT"/>
+                  <dgm:param type="chAlign" val="l"/>
+                </dgm:alg>
+              </dgm:if>
+              <dgm:else name="Name10">
+                <dgm:alg type="hierChild">
+                  <dgm:param type="linDir" val="fromT"/>
+                  <dgm:param type="chAlign" val="r"/>
+                </dgm:alg>
+              </dgm:else>
+            </dgm:choose>
+            <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+              <dgm:adjLst/>
+            </dgm:shape>
+            <dgm:presOf/>
+            <dgm:constrLst/>
+            <dgm:ruleLst/>
+            <dgm:forEach name="repeat" axis="ch">
+              <dgm:forEach name="Name11" axis="self" ptType="parTrans" cnt="1">
+                <dgm:layoutNode name="conn2-1">
+                  <dgm:choose name="Name12">
+                    <dgm:if name="Name13" func="var" arg="dir" op="equ" val="norm">
+                      <dgm:alg type="conn">
+                        <dgm:param type="dim" val="1D"/>
+                        <dgm:param type="begPts" val="midR"/>
+                        <dgm:param type="endPts" val="midL"/>
+                        <dgm:param type="endSty" val="noArr"/>
+                      </dgm:alg>
+                    </dgm:if>
+                    <dgm:else name="Name14">
+                      <dgm:alg type="conn">
+                        <dgm:param type="dim" val="1D"/>
+                        <dgm:param type="begPts" val="midL"/>
+                        <dgm:param type="endPts" val="midR"/>
+                        <dgm:param type="endSty" val="noArr"/>
+                      </dgm:alg>
+                    </dgm:else>
+                  </dgm:choose>
+                  <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="conn" r:blip="">
+                    <dgm:adjLst/>
+                  </dgm:shape>
+                  <dgm:presOf axis="self"/>
+                  <dgm:constrLst>
+                    <dgm:constr type="w" val="1"/>
+                    <dgm:constr type="h" val="5"/>
+                    <dgm:constr type="connDist"/>
+                    <dgm:constr type="begPad"/>
+                    <dgm:constr type="endPad"/>
+                    <dgm:constr type="userA" for="ch" refType="connDist"/>
+                  </dgm:constrLst>
+                  <dgm:ruleLst/>
+                  <dgm:layoutNode name="connTx">
+                    <dgm:alg type="tx">
+                      <dgm:param type="autoTxRot" val="grav"/>
+                    </dgm:alg>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="rect" r:blip="" hideGeom="1">
+                      <dgm:adjLst/>
+                    </dgm:shape>
+                    <dgm:presOf axis="self"/>
+                    <dgm:constrLst>
+                      <dgm:constr type="userA"/>
+                      <dgm:constr type="w" refType="userA" fact="0.05"/>
+                      <dgm:constr type="h" refType="userA" fact="0.05"/>
+                      <dgm:constr type="lMarg" val="1"/>
+                      <dgm:constr type="rMarg" val="1"/>
+                      <dgm:constr type="tMarg"/>
+                      <dgm:constr type="bMarg"/>
+                    </dgm:constrLst>
+                    <dgm:ruleLst>
+                      <dgm:rule type="h" val="NaN" fact="0.25" max="NaN"/>
+                      <dgm:rule type="w" val="NaN" fact="0.8" max="NaN"/>
+                      <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+                    </dgm:ruleLst>
+                  </dgm:layoutNode>
+                </dgm:layoutNode>
+              </dgm:forEach>
+              <dgm:forEach name="Name15" axis="self" ptType="node">
+                <dgm:layoutNode name="root2">
+                  <dgm:choose name="Name16">
+                    <dgm:if name="Name17" func="var" arg="dir" op="equ" val="norm">
+                      <dgm:alg type="hierRoot">
+                        <dgm:param type="hierAlign" val="lCtrCh"/>
+                      </dgm:alg>
+                    </dgm:if>
+                    <dgm:else name="Name18">
+                      <dgm:alg type="hierRoot">
+                        <dgm:param type="hierAlign" val="rCtrCh"/>
+                      </dgm:alg>
+                    </dgm:else>
+                  </dgm:choose>
+                  <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+                    <dgm:adjLst/>
+                  </dgm:shape>
+                  <dgm:presOf/>
+                  <dgm:constrLst/>
+                  <dgm:ruleLst/>
+                  <dgm:layoutNode name="LevelTwoTextNode">
+                    <dgm:varLst>
+                      <dgm:chPref val="3"/>
+                    </dgm:varLst>
+                    <dgm:alg type="tx"/>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="roundRect" r:blip="">
+                      <dgm:adjLst>
+                        <dgm:adj idx="1" val="0.1"/>
+                      </dgm:adjLst>
+                    </dgm:shape>
+                    <dgm:presOf axis="self"/>
+                    <dgm:constrLst>
+                      <dgm:constr type="tMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="bMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="lMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="rMarg" refType="primFontSz" fact="0.05"/>
+                    </dgm:constrLst>
+                    <dgm:ruleLst>
+                      <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+                    </dgm:ruleLst>
+                  </dgm:layoutNode>
+                  <dgm:layoutNode name="level3hierChild">
+                    <dgm:choose name="Name19">
+                      <dgm:if name="Name20" func="var" arg="dir" op="equ" val="norm">
+                        <dgm:alg type="hierChild">
+                          <dgm:param type="linDir" val="fromT"/>
+                          <dgm:param type="chAlign" val="l"/>
+                        </dgm:alg>
+                      </dgm:if>
+                      <dgm:else name="Name21">
+                        <dgm:alg type="hierChild">
+                          <dgm:param type="linDir" val="fromT"/>
+                          <dgm:param type="chAlign" val="r"/>
+                        </dgm:alg>
+                      </dgm:else>
+                    </dgm:choose>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+                      <dgm:adjLst/>
+                    </dgm:shape>
+                    <dgm:presOf/>
+                    <dgm:constrLst/>
+                    <dgm:ruleLst/>
+                    <dgm:forEach name="Name22" ref="repeat"/>
+                  </dgm:layoutNode>
+                </dgm:layoutNode>
+              </dgm:forEach>
+            </dgm:forEach>
+          </dgm:layoutNode>
+        </dgm:layoutNode>
+      </dgm:forEach>
+    </dgm:forEach>
+  </dgm:layoutNode>
+</dgm:layoutDef>
+</file>
+
+<file path=xl/diagrams/quickStyle1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:styleDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="simple" pri="10100"/>
+  </dgm:catLst>
+  <dgm:scene3d>
+    <a:camera prst="orthographicFront"/>
+    <a:lightRig rig="threePt" dir="t"/>
+  </dgm:scene3d>
+  <dgm:styleLbl name="node0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="tx1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+</dgm:styleDef>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>234462</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="다이어그램 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD2F604C-D941-3B08-8101-E3FF58C5C0B3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/diagram">
+          <dgm:relIds xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:dm="rId1" r:lo="rId2" r:qs="rId3" r:cs="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1700,610 +8096,610 @@
   <dimension ref="A1:C136"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" style="30" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" style="21" customWidth="1"/>
     <col min="2" max="2" width="32.9140625" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A3" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A3" s="31" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" s="32" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" s="32" t="s">
+    <row r="8" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A8" s="22" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A8" s="31" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" s="21" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" s="30" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="30" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" s="23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" s="30" t="s">
+    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A15" s="24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" s="32" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" s="25" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A15" s="33" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="26" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A16" s="34" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" s="26" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" s="35" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="26" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" s="35" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" s="26" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" s="35" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" s="26" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" s="35" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" s="26" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" s="35" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="26" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" s="35" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="26" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" s="35" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" s="35" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" s="26" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" s="35" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" s="26" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" s="35" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" s="23" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" s="35" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" s="21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A30" s="32" t="s">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="21" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" s="30" t="s">
+    <row r="36" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A36" s="22" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" s="30" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" s="30" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A36" s="31" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" s="30" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="23" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" s="32" t="s">
+    <row r="43" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A43" s="22" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" s="30" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" s="21" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" s="32" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" s="21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A43" s="31" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" s="21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A44" s="30" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" s="30" t="s">
+    <row r="50" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A50" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A51" s="24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" s="30" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="27"/>
+      <c r="B52" s="18" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" s="32" t="s">
+      <c r="C52" s="18" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A50" s="33" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A51" s="33" t="s">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" s="28" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="36"/>
-      <c r="B52" s="27" t="s">
+      <c r="B53" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C52" s="27" t="s">
+      <c r="C53" s="19" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="37" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B54" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C54" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="37" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B55" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="C54" s="28" t="s">
+      <c r="C55" s="19" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="37" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B56" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="C55" s="28" t="s">
+      <c r="C56" s="19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="37" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B57" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C56" s="28" t="s">
+      <c r="C57" s="19" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="37" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="B57" s="28" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="C57" s="28" t="s">
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="26" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="32" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="26" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="34" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="26" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="35" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" s="26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="35" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" s="26" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="35" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" s="26" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A65" s="35" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" s="26" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A66" s="35" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" s="26" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A67" s="35" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A70" s="26" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A68" s="35" t="s">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A71" s="26" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" s="35" t="s">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A72" s="26" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A70" s="35" t="s">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A73" s="26" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A71" s="35" t="s">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A74" s="26" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A72" s="35" t="s">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A75" s="26" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A73" s="35" t="s">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A77" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A78" s="21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A74" s="35" t="s">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A79" s="21" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A75" s="35" t="s">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A80" s="21" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A77" s="32" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A78" s="30" t="s">
+    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A82" s="24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="30" t="s">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A83" s="23" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A80" s="30" t="s">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A84" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A82" s="33" t="s">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A85" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A83" s="32" t="s">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A86" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A84" s="32" t="s">
+    <row r="88" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A88" s="22" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A85" s="32" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A89" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A86" s="30" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A90" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A88" s="31" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A91" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A89" s="30" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A93" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A90" s="30" t="s">
+    <row r="95" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A95" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A91" s="30" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A96" s="21" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A97" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A93" s="32" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A98" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A95" s="31" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A100" s="23" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A96" s="30" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A97" s="30" t="s">
+    <row r="102" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A102" s="22" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A98" s="30" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A103" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A100" s="32" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A104" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A102" s="31" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A106" s="23" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A103" s="30" t="s">
+    <row r="108" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A108" s="22" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A104" s="30" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A110" s="21" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A106" s="32" t="s">
+    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A112" s="24" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A108" s="31" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A114" s="27" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A110" s="30" t="s">
+      <c r="B114" s="18" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A112" s="33" t="s">
+      <c r="C114" s="18" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A114" s="36" t="s">
+    <row r="115" spans="1:3" ht="34" x14ac:dyDescent="0.45">
+      <c r="A115" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B114" s="27" t="s">
+      <c r="B115" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="C114" s="27" t="s">
+      <c r="C115" s="19" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="34" x14ac:dyDescent="0.45">
-      <c r="A115" s="37" t="s">
+    <row r="116" spans="1:3" ht="51" x14ac:dyDescent="0.45">
+      <c r="A116" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="B115" s="28" t="s">
+      <c r="B116" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C115" s="28" t="s">
+      <c r="C116" s="19" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="51" x14ac:dyDescent="0.45">
-      <c r="A116" s="37" t="s">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A118" s="21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A120" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="B116" s="28" t="s">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A121" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C116" s="28" t="s">
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A122" s="21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A118" s="30" t="s">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A123" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A124" s="21" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A126" s="23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A128" s="24" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="B129" s="29" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A130" s="32" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A120" s="33" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A121" s="30" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A122" s="30" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A123" s="30" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A124" s="30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A126" s="32" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A128" s="33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" s="40" t="s">
+      <c r="B130" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="B129" s="38" t="s">
+    </row>
+    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+      <c r="A131" s="32" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A130" s="41" t="s">
+      <c r="B131" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="B130" s="39" t="s">
+    </row>
+    <row r="132" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A132" s="32" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.45">
-      <c r="A131" s="41" t="s">
+      <c r="B132" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="B131" s="39" t="s">
+    </row>
+    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+      <c r="A133" s="32" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A132" s="41" t="s">
+      <c r="B133" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B132" s="39" t="s">
+    </row>
+    <row r="134" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A134" s="32" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.45">
-      <c r="A133" s="41" t="s">
+      <c r="B134" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="B133" s="39" t="s">
+    </row>
+    <row r="135" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A135" s="32" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A134" s="41" t="s">
+      <c r="B135" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="B134" s="39" t="s">
+    </row>
+    <row r="136" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A136" s="32" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A135" s="41" t="s">
+      <c r="B136" s="30" t="s">
         <v>173</v>
-      </c>
-      <c r="B135" s="39" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A136" s="41" t="s">
-        <v>175</v>
-      </c>
-      <c r="B136" s="39" t="s">
-        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2327,117 +8723,117 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.9140625" style="43" customWidth="1"/>
-    <col min="2" max="2" width="63.83203125" style="43" customWidth="1"/>
-    <col min="3" max="3" width="22" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.25" style="43" customWidth="1"/>
+    <col min="1" max="1" width="25.9140625" style="34" customWidth="1"/>
+    <col min="2" max="2" width="21.58203125" style="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22" style="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.25" style="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="42" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C2" s="37">
+        <v>46274</v>
+      </c>
+      <c r="D2" s="35"/>
+    </row>
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="37">
+        <v>46274</v>
+      </c>
+      <c r="D3" s="35"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="37">
+        <v>46274</v>
+      </c>
+      <c r="D4" s="35"/>
+    </row>
+    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A5" s="36" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="46">
-        <v>46274</v>
-      </c>
-      <c r="D2" s="44"/>
-    </row>
-    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A3" s="45" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="37">
+        <v>46275</v>
+      </c>
+      <c r="D5" s="35"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="37">
+        <v>46275</v>
+      </c>
+      <c r="D6" s="35"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="B7" s="35"/>
+      <c r="C7" s="37">
+        <v>46276</v>
+      </c>
+      <c r="D7" s="35"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="46">
-        <v>46274</v>
-      </c>
-      <c r="D3" s="44"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="44" t="s">
-        <v>184</v>
-      </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="46">
-        <v>46274</v>
-      </c>
-      <c r="D4" s="44"/>
-    </row>
-    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A5" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="46">
-        <v>46275</v>
-      </c>
-      <c r="D5" s="44"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="44" t="s">
+      <c r="B8" s="35"/>
+      <c r="C8" s="37">
+        <v>46276</v>
+      </c>
+      <c r="D8" s="35"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="35" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="46">
-        <v>46275</v>
-      </c>
-      <c r="D6" s="44"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="44" t="s">
+      <c r="B9" s="35"/>
+      <c r="C9" s="37">
+        <v>46276</v>
+      </c>
+      <c r="D9" s="35"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="35" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="46">
-        <v>46276</v>
-      </c>
-      <c r="D7" s="44"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="46">
-        <v>46276</v>
-      </c>
-      <c r="D8" s="44"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="46">
-        <v>46276</v>
-      </c>
-      <c r="D9" s="44"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="46">
+      <c r="B10" s="35"/>
+      <c r="C10" s="37">
         <v>46279</v>
       </c>
-      <c r="D10" s="44"/>
+      <c r="D10" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2463,278 +8859,278 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="38" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="24" t="s">
-        <v>20</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="10"/>
       <c r="G2" s="11"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="25"/>
+      <c r="A3" s="39"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G3" s="12"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="25"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="4" t="s">
-        <v>2</v>
+        <v>194</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="3"/>
       <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="25"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="3"/>
       <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="25"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="26"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="18" t="s">
-        <v>21</v>
+      <c r="A8" s="41" t="s">
+        <v>20</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="19"/>
+      <c r="A9" s="42"/>
       <c r="B9" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="3"/>
       <c r="G9" s="12"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="19"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="12"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="19"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="3"/>
       <c r="G11" s="12"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="20"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="15"/>
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="s">
-        <v>22</v>
+      <c r="A13" s="44" t="s">
+        <v>21</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
     </row>
     <row r="14" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A14" s="22"/>
+      <c r="A14" s="45"/>
       <c r="B14" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G14" s="12"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="22"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="23"/>
+      <c r="A16" s="46"/>
       <c r="B16" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>13</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>14</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="15"/>
       <c r="G16" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2750,11 +9146,33 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FF030F-F06A-41B1-B87E-BFF5ED98AB05}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="47" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="48" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="64" x14ac:dyDescent="0.45">
+      <c r="A2" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/project_2/project2_project status(C2)xlsx.xlsx
+++ b/project_2/project2_project status(C2)xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2028125F-BBE8-410F-A8D7-4BF23F86D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100AD062-9B8D-476D-9705-B9515056855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="198">
   <si>
     <t>reward</t>
   </si>
@@ -936,6 +936,14 @@
   </si>
   <si>
     <t>각 가지가 참·거짓을 판정할 수 있는 명제로 서술되어 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Funnel &amp; North Star Framework</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>North Star Metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3332,6 +3340,533 @@
         </a:p>
       </dgm:t>
     </dgm:pt>
+    <dgm:pt modelId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Profile(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>고객 정보</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{FF7B4EF7-F173-446C-B7FC-76DF9BD7C3B7}" type="parTrans" cxnId="{94CE50DD-5A01-4009-B770-500D579F6261}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{59629897-8AC3-4B42-ABE4-2D4F4203E3F5}" type="sibTrans" cxnId="{94CE50DD-5A01-4009-B770-500D579F6261}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>성별</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" type="parTrans" cxnId="{9457F039-2CF0-400D-9C71-03F7FA015A09}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{62737957-12F2-4387-9BC7-5F56D2832693}" type="sibTrans" cxnId="{9457F039-2CF0-400D-9C71-03F7FA015A09}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{33570384-A605-4DA1-B67B-2279EF2BEACD}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" type="parTrans" cxnId="{415577E8-A702-41BC-965B-528E316FA7F6}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8DF4D672-D274-4D39-8836-B1757F2C493E}" type="sibTrans" cxnId="{415577E8-A702-41BC-965B-528E316FA7F6}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{80595224-034E-4CE4-8A96-DF4078F87D5A}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>나이</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" type="parTrans" cxnId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{66DC472F-0C00-4597-B38A-CB794F5A3548}" type="sibTrans" cxnId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득이 높으면</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>만불</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>+) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" type="parTrans" cxnId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{9BD685D9-FACC-4933-B23B-7AEB4A4D12BF}" type="sibTrans" cxnId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1">
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>여성이면 남성보다 완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" type="parTrans" cxnId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BD1CDDA8-026D-47C8-97D3-4F862427D632}" type="sibTrans" cxnId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:srgbClr val="5B9BD5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>나이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(54) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은면 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" type="parTrans" cxnId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{0F15BF54-44D9-44C8-9D21-7047F7863151}" type="sibTrans" cxnId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
     <dgm:pt modelId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" type="pres">
       <dgm:prSet presAssocID="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" presName="diagram" presStyleCnt="0">
         <dgm:presLayoutVars>
@@ -3349,7 +3884,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" type="pres">
-      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="1" custScaleX="156668">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="2" custScaleX="156668">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3361,11 +3896,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}" type="pres">
-      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" type="pres">
-      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{01253263-E07D-4F9F-8798-5E3E260C947E}" type="pres">
@@ -3373,7 +3908,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" type="pres">
-      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="5">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="8">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3385,11 +3920,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" type="pres">
-      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" type="pres">
-      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" type="pres">
@@ -3397,7 +3932,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" type="pres">
-      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="8" custScaleX="313336" custLinFactNeighborX="-620">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="11" custScaleX="313336" custLinFactNeighborX="-620">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3409,11 +3944,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" type="pres">
-      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" type="pres">
-      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" type="pres">
@@ -3421,7 +3956,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" type="pres">
-      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="5">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="8">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3433,11 +3968,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" type="pres">
-      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" type="pres">
-      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" type="pres">
@@ -3445,7 +3980,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" type="pres">
-      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3457,11 +3992,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}" type="pres">
-      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" type="pres">
-      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" type="pres">
@@ -3469,7 +4004,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" type="pres">
-      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="5">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="8">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3481,11 +4016,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" type="pres">
-      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" type="pres">
-      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" type="pres">
@@ -3493,7 +4028,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" type="pres">
-      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3505,11 +4040,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}" type="pres">
-      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" type="pres">
-      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{F3B7EAB8-F828-469D-957A-9C0140751550}" type="pres">
@@ -3517,7 +4052,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}" type="pres">
-      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="5">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="8">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3529,11 +4064,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" type="pres">
-      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" type="pres">
-      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" type="pres">
@@ -3541,7 +4076,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" type="pres">
-      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3553,11 +4088,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}" type="pres">
-      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" type="pres">
-      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" type="pres">
@@ -3565,7 +4100,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{2D542640-C237-42B5-8470-73084719F8F3}" type="pres">
-      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3577,11 +4112,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" type="pres">
-      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" type="pres">
-      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" type="pres">
@@ -3589,7 +4124,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}" type="pres">
-      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3601,11 +4136,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" type="pres">
-      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" type="pres">
-      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" type="pres">
@@ -3613,7 +4148,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{220D319D-36C0-42A0-A946-F197C4269C14}" type="pres">
-      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3625,11 +4160,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{4332858F-88A7-466E-8722-8833A7B96598}" type="pres">
-      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" type="pres">
-      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="5"/>
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="8"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{41714DC3-F3A7-41BB-8371-656B34451539}" type="pres">
@@ -3637,7 +4172,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" type="pres">
-      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="5">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="8">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3649,11 +4184,11 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" type="pres">
-      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{274B025F-D16B-4968-87D0-380BD22343AE}" type="pres">
-      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="11"/>
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" type="pres">
@@ -3661,7 +4196,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" type="pres">
-      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="8" custScaleX="313336">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="11" custScaleX="313336">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3672,31 +4207,219 @@
       <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="level3hierChild" presStyleCnt="0"/>
       <dgm:spPr/>
     </dgm:pt>
+    <dgm:pt modelId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="root1" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="1" presStyleCnt="2" custScaleX="156890" custLinFactNeighborX="-14777">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="level2hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" type="pres">
+      <dgm:prSet presAssocID="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" type="pres">
+      <dgm:prSet presAssocID="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="5" presStyleCnt="8" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" type="pres">
+      <dgm:prSet presAssocID="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="8" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" type="pres">
+      <dgm:prSet presAssocID="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="8" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="8" presStyleCnt="11" custScaleX="313273" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{78142362-D1E5-4930-A6C3-A3472F8177FC}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" type="pres">
+      <dgm:prSet presAssocID="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" type="pres">
+      <dgm:prSet presAssocID="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="6" presStyleCnt="8" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{55492AE0-989E-4368-96E6-8609B6786079}" type="pres">
+      <dgm:prSet presAssocID="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="9" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" type="pres">
+      <dgm:prSet presAssocID="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="9" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="9" presStyleCnt="11" custScaleX="313273" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A65938CF-8D2A-430E-BD5D-0E3A94E0D736}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" type="pres">
+      <dgm:prSet presAssocID="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" type="pres">
+      <dgm:prSet presAssocID="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0903B9B2-87B3-423C-B698-A23126107E5E}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="7" presStyleCnt="8" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}" type="pres">
+      <dgm:prSet presAssocID="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="10" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" type="pres">
+      <dgm:prSet presAssocID="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="10" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="10" presStyleCnt="11" custScaleX="313273">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr>
+        <a:xfrm>
+          <a:off x="3519732" y="4080309"/>
+          <a:ext cx="2252419" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </dgm:spPr>
+    </dgm:pt>
+    <dgm:pt modelId="{8554999F-A756-45D0-8A9C-D7615B2C3AF7}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
   </dgm:ptLst>
   <dgm:cxnLst>
     <dgm:cxn modelId="{E716BF02-E552-4CCD-89CD-A5B0B6E9EC70}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" srcOrd="1" destOrd="0" parTransId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" sibTransId="{D56ED9E6-07E6-476D-B72A-1DAC45654595}"/>
+    <dgm:cxn modelId="{99AA9D0D-42AF-40A4-AEA7-96603169FD06}" type="presOf" srcId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" destId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{AF850C0E-477F-45E3-A0A3-1F4786C24FFD}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{274B025F-D16B-4968-87D0-380BD22343AE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{6789530F-FB45-46BA-9B1D-3B3341D4D748}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{ED5992BD-91A0-44DC-B026-C230E027754F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{D62D4711-4853-49C5-AD88-6A4C204E26FD}" type="presOf" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{E147F012-F227-46EA-B01A-D20475D3B67D}" type="presOf" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" srcOrd="0" destOrd="0" parTransId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" sibTransId="{33CA151E-3B69-4314-B123-3297DFC7D670}"/>
+    <dgm:cxn modelId="{9AE49117-A534-41D2-B551-473D96BC5FE7}" type="presOf" srcId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" destId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{C5516619-C5B2-4288-84CD-67C055A97476}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" srcOrd="2" destOrd="0" parTransId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" sibTransId="{05412BF9-284B-4F1C-86AC-AF524BDD7D14}"/>
+    <dgm:cxn modelId="{2598091B-CB6C-4630-8FCC-1A5A75233A10}" type="presOf" srcId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" destId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}" srcId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" destId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" srcOrd="0" destOrd="0" parTransId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" sibTransId="{BD1CDDA8-026D-47C8-97D3-4F862427D632}"/>
+    <dgm:cxn modelId="{6455C92C-AEDC-406D-9314-14128F0262F1}" type="presOf" srcId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" destId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{814B5B2D-0636-46D6-8357-3E465A736B44}" type="presOf" srcId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" destId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F8DDFC2D-2786-40D0-B273-9C978A0F6003}" type="presOf" srcId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" destId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{598EE134-21B8-4BC4-B868-2937D8E35E75}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{806C8330-1E37-41AD-AEEE-3552A4162510}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9457F039-2CF0-400D-9C71-03F7FA015A09}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" srcOrd="0" destOrd="0" parTransId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" sibTransId="{62737957-12F2-4387-9BC7-5F56D2832693}"/>
     <dgm:cxn modelId="{11932F3D-BA9B-441A-8939-E3C049AD81D3}" type="presOf" srcId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" destId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{23EFEB5C-12C0-41AD-97DC-8B6DAC0830C7}" type="presOf" srcId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" destId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{89570F43-E429-40CF-A897-90E077418661}" type="presOf" srcId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" destId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D4A95A63-993F-49BA-844C-081D17E5005A}" type="presOf" srcId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" destId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{649BBD44-4CFF-49CE-B5C2-02F87A124FCF}" type="presOf" srcId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" destId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{719F1E48-19AF-416D-BC2E-82961DFA1755}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{D92FE84D-8344-484F-96C7-CD04C772FFCE}" type="presOf" srcId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9FD5D850-9393-4E82-9B60-F344E814296E}" type="presOf" srcId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" destId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" srcOrd="2" destOrd="0" parTransId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" sibTransId="{DE75E50D-DFA6-418B-9C06-95A5C3944847}"/>
     <dgm:cxn modelId="{8CEC1554-B055-464F-AC47-FCFB34B80966}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{3E881757-362F-489E-B630-0D8A32984B2B}" srcOrd="3" destOrd="0" parTransId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" sibTransId="{278E719C-4D84-4910-9C25-3DCD78815614}"/>
     <dgm:cxn modelId="{F7115254-B2DB-4711-9B96-1797D64046C8}" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" srcOrd="0" destOrd="0" parTransId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" sibTransId="{827A2A25-BF22-45D1-8C10-6D340F70C6A1}"/>
     <dgm:cxn modelId="{CAEBC875-3C11-4DF4-B17E-40CDB162EBA4}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{26B40478-8828-42BA-B106-CA1C827BA177}" type="presOf" srcId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" destId="{55492AE0-989E-4368-96E6-8609B6786079}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7D8F6358-B9F1-4D8C-BE58-5881541E729C}" type="presOf" srcId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" destId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" srcOrd="1" destOrd="0" parTransId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" sibTransId="{E023194C-F95D-4763-92F5-F1ECD4BC9C73}"/>
     <dgm:cxn modelId="{D2FA5A79-1C6F-4BA4-9743-73F806A7B41B}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{222A087A-B882-4E51-91BF-D7CCCD051844}" type="presOf" srcId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" destId="{4D54B04B-F98B-4577-8925-91ECEF877996}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A9F11C7D-D01E-43D8-AD5C-A31108B40C7D}" type="presOf" srcId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" destId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7322667D-69E2-4F51-9B08-CC032291FF5E}" type="presOf" srcId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" destId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2797ED7D-20C0-4797-8100-2F2E86906BAA}" type="presOf" srcId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" destId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" srcOrd="0" destOrd="0" parTransId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" sibTransId="{213EC674-33B2-46B5-97B4-B78DD7CC6633}"/>
     <dgm:cxn modelId="{9E93E484-6F94-455F-905B-83CCF7FF2B2F}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{BE014B86-3D98-439A-9866-D73914E0EE7E}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3EC75F87-8E50-46E6-B6AC-7DC42AF700E7}" type="presOf" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{604F8188-5220-4BBD-B051-AE258F4786C5}" type="presOf" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{9554478A-1EB0-4AAA-ADAE-9FB3873C43EB}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{8462148B-1DD3-441F-B63F-6F0F33CA55E6}" type="presOf" srcId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" destId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
@@ -3704,10 +4427,12 @@
     <dgm:cxn modelId="{00C77A8E-6B70-42A2-9561-C73F86BE4CF8}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{CF369B92-780C-46D0-9ED6-7B81FBADD727}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{17E63997-D9CE-4D39-AE2E-A3AE0D1284BC}" type="presOf" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}" srcId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" destId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" srcOrd="0" destOrd="0" parTransId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" sibTransId="{0F15BF54-44D9-44C8-9D21-7047F7863151}"/>
     <dgm:cxn modelId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" srcOrd="0" destOrd="0" parTransId="{61B28454-54A2-4A23-B946-6072BC34D484}" sibTransId="{F87A8A7F-0D3D-4479-81E7-4B421A7751B7}"/>
     <dgm:cxn modelId="{24D5F7A1-BC55-49BA-AD3A-9E7950427D56}" type="presOf" srcId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" destId="{2D542640-C237-42B5-8470-73084719F8F3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" srcOrd="0" destOrd="0" parTransId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" sibTransId="{B0E34315-446D-43CA-9C1A-43AC03C7FA4E}"/>
     <dgm:cxn modelId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" srcOrd="0" destOrd="0" parTransId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" sibTransId="{B9BFC1E1-36FA-4DFA-A7FB-937425619DD8}"/>
+    <dgm:cxn modelId="{07E8A4AA-9A8A-4504-A01B-F5E592908ED0}" type="presOf" srcId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" destId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" srcOrd="0" destOrd="0" parTransId="{8FA42352-D834-44A6-A154-3CB76BE81B68}" sibTransId="{71F878CA-1A36-404F-978F-D8724DEDCCAF}"/>
     <dgm:cxn modelId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" srcOrd="4" destOrd="0" parTransId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" sibTransId="{B5F3BFB9-0C8D-4ED3-BB39-6E65AD6E6202}"/>
     <dgm:cxn modelId="{A37199AF-6B7B-4D63-9BED-72A4088E31D7}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
@@ -3715,15 +4440,21 @@
     <dgm:cxn modelId="{9E72F2B5-B38B-4682-A94E-6A0A12C507BD}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{C2E5C8C2-39E3-4172-B04E-F41ADFDEB387}" type="presOf" srcId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" destId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{FB2B60CC-0744-4CF3-81D8-7AD4A3610137}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{227E0FEF-1368-4562-AD55-940C6A450E91}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}" srcId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" destId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" srcOrd="0" destOrd="0" parTransId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" sibTransId="{9BD685D9-FACC-4933-B23B-7AEB4A4D12BF}"/>
     <dgm:cxn modelId="{A20F76D0-7BCB-45E8-B360-790EB5F29686}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{DBF535D2-BD92-4672-8867-EA84BC5763AA}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{2440BBD3-B375-44FF-872D-AB1B780F978C}" type="presOf" srcId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" destId="{106C3051-36E0-4DB2-B006-BD51244834C6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" srcOrd="3" destOrd="0" parTransId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" sibTransId="{81FA6521-2044-4D8B-A3F2-96C820EAF9F1}"/>
     <dgm:cxn modelId="{22675FDB-D57E-40A9-8DB8-24BDE2145037}" type="presOf" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{D9CA61DC-2D30-46B4-A093-77D4B2F30BE9}" type="presOf" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{146FB508-948A-484E-B54F-2A63CE5492FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{94CE50DD-5A01-4009-B770-500D579F6261}" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" srcOrd="1" destOrd="0" parTransId="{FF7B4EF7-F173-446C-B7FC-76DF9BD7C3B7}" sibTransId="{59629897-8AC3-4B42-ABE4-2D4F4203E3F5}"/>
+    <dgm:cxn modelId="{36CDA4DE-2626-4984-9CC3-17FFAB24499D}" type="presOf" srcId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" destId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{4FE23EDF-13FE-4703-91E6-6C903EDF68FE}" type="presOf" srcId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" destId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{3D57FDE0-4E64-475C-A9CE-314E2DD7D40C}" type="presOf" srcId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" destId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{36020EE3-17F3-4E72-86E8-11CC0757B176}" type="presOf" srcId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" destId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{CCFD01E6-B250-4974-8ACC-B4488D55724F}" type="presOf" srcId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" destId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{415577E8-A702-41BC-965B-528E316FA7F6}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" srcOrd="1" destOrd="0" parTransId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" sibTransId="{8DF4D672-D274-4D39-8836-B1757F2C493E}"/>
+    <dgm:cxn modelId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" srcOrd="2" destOrd="0" parTransId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" sibTransId="{66DC472F-0C00-4597-B38A-CB794F5A3548}"/>
     <dgm:cxn modelId="{6AA869F1-2370-47CB-8892-04E1C8E66198}" type="presOf" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{D46966F4-1F6B-44AE-BBA7-9D94EA384573}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{4332858F-88A7-466E-8722-8833A7B96598}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{6BB77CF6-5C09-47BD-BAE8-C3CAB397D44B}" type="presOf" srcId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" destId="{220D319D-36C0-42A0-A946-F197C4269C14}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
@@ -3797,6 +4528,39 @@
     <dgm:cxn modelId="{E595B179-46DA-4256-9CC9-35B70B57CAE1}" type="presParOf" srcId="{5B364536-61C6-4C87-983E-3D7708A352A0}" destId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{BAEA4C6F-55B1-4D11-A93D-613622995B8E}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
     <dgm:cxn modelId="{E7A12BF5-6203-42EB-8DFF-6FE7ABF53C31}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{98E7E4BB-43E7-4635-B1B5-7AAB6FB148D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{75BF1823-0EE5-4D7A-B576-AD473639D45E}" type="presParOf" srcId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" destId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{95B9CA0F-C69A-4F0A-8B5B-F813CBC58E05}" type="presParOf" srcId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" destId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2CC52935-99B2-4F74-9854-B27711434E67}" type="presParOf" srcId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" destId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{EB167583-6950-4ED9-B790-4EA12AEEFBFB}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{172A04DF-ACFF-4FDF-AD08-027416307FA5}" type="presParOf" srcId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" destId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B83CE91A-3936-4D68-B5A0-214760472BBD}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5A796D3D-E4AB-41E9-A1B6-F42A12CC5928}" type="presParOf" srcId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" destId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D7D3A8FB-7EBD-451D-9A12-7697CE6D42EE}" type="presParOf" srcId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" destId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{0FECD05A-0D68-496F-B1A6-1AF5C8B53D98}" type="presParOf" srcId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" destId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{370BECC2-9BC0-4671-9B1D-9499F0A9A5F8}" type="presParOf" srcId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" destId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6DF0238A-F592-4BFA-9785-F323818E9F5B}" type="presParOf" srcId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" destId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{774DA7F0-06E5-4859-9234-EB450891EFEA}" type="presParOf" srcId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" destId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{75B85929-83F3-4CAC-9555-19331703AA5F}" type="presParOf" srcId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" destId="{78142362-D1E5-4930-A6C3-A3472F8177FC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{ADA83DF1-FFF5-46E9-A03E-F159850BABC1}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{73604811-188B-48D5-B552-8CB1A83C7ABD}" type="presParOf" srcId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" destId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3AA0550E-3751-4E63-9292-9699CC1D1F1C}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{37B6054D-825F-40CB-B57D-9228B48F6F9B}" type="presParOf" srcId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" destId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CA8DA526-C626-47E2-A139-B33B566F8665}" type="presParOf" srcId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" destId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9C0347E4-C658-4BD1-ADB5-9423E949F6FB}" type="presParOf" srcId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" destId="{55492AE0-989E-4368-96E6-8609B6786079}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CE8010B9-8D41-457A-81B8-7CE369F49574}" type="presParOf" srcId="{55492AE0-989E-4368-96E6-8609B6786079}" destId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2DD874FE-71FA-4496-B731-7D0EDD19E262}" type="presParOf" srcId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" destId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{54E0DE47-D516-4912-B7E2-5F85E1F1DC00}" type="presParOf" srcId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" destId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5087B92D-35C5-4473-98AF-74964C81D5F5}" type="presParOf" srcId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" destId="{A65938CF-8D2A-430E-BD5D-0E3A94E0D736}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{FA689ACA-D620-4079-8B75-9E47B0845C5D}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6BC74307-6578-4EA8-9506-340B08821961}" type="presParOf" srcId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" destId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C41B66F3-C317-4D3A-A79F-2CF01A5DA187}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{0903B9B2-87B3-423C-B698-A23126107E5E}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6C106DE6-4B2D-4A80-B427-FEE163EF3D9E}" type="presParOf" srcId="{0903B9B2-87B3-423C-B698-A23126107E5E}" destId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2EEE09BA-D37F-4E0F-97E0-888FF9D4EF69}" type="presParOf" srcId="{0903B9B2-87B3-423C-B698-A23126107E5E}" destId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4C10D8C5-7419-4D3A-AB39-C66D7D1336F1}" type="presParOf" srcId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" destId="{4D54B04B-F98B-4577-8925-91ECEF877996}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{89771D1C-93C2-4DA6-92E8-C0D1F12ECD74}" type="presParOf" srcId="{4D54B04B-F98B-4577-8925-91ECEF877996}" destId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{AFBE5A2C-758A-4C31-A17B-9FEF910CE064}" type="presParOf" srcId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" destId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{19CF9FF2-D3B9-498D-8E29-02BAD80A8840}" type="presParOf" srcId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" destId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{0F7DF2FB-6B4F-4A35-AAB9-D847481323C9}" type="presParOf" srcId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" destId="{8554999F-A756-45D0-8A9C-D7615B2C3AF7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
   </dgm:cxnLst>
   <dgm:bg>
     <a:solidFill>
@@ -3833,8 +4597,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="244948" y="1988314"/>
-          <a:ext cx="1545781" cy="493330"/>
+          <a:off x="685922" y="1430308"/>
+          <a:ext cx="1110823" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -3933,8 +4697,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="259397" y="2002763"/>
-        <a:ext cx="1516883" cy="464432"/>
+        <a:off x="696305" y="1440691"/>
+        <a:ext cx="1090057" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -3944,8 +4708,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="975814" y="1232219"/>
-          <a:ext cx="2024496" cy="19865"/>
+          <a:off x="1211134" y="886915"/>
+          <a:ext cx="1454835" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -3956,10 +4720,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="2024496" y="9932"/>
+                <a:pt x="1454835" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4018,8 +4782,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1937449" y="1191539"/>
-        <a:ext cx="101224" cy="101224"/>
+        <a:off x="1902181" y="857733"/>
+        <a:ext cx="72741" cy="72741"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -4029,8 +4793,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2185394" y="2659"/>
-          <a:ext cx="986660" cy="493330"/>
+          <a:off x="2080358" y="3384"/>
+          <a:ext cx="709030" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4105,8 +4869,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2199843" y="17108"/>
-        <a:ext cx="957762" cy="464432"/>
+        <a:off x="2090741" y="13767"/>
+        <a:ext cx="688264" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -4116,8 +4880,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3172055" y="239391"/>
-          <a:ext cx="388547" cy="19865"/>
+          <a:off x="2789389" y="173453"/>
+          <a:ext cx="279216" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4128,10 +4892,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="388547" y="9932"/>
+                <a:pt x="279216" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4190,8 +4954,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3356615" y="239611"/>
-        <a:ext cx="19427" cy="19427"/>
+        <a:off x="2922016" y="173662"/>
+        <a:ext cx="13960" cy="13960"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -4201,8 +4965,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3560602" y="2659"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3068605" y="3384"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4301,8 +5065,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3575051" y="17108"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3078988" y="13767"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -4312,8 +5076,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1251956" y="1515884"/>
-          <a:ext cx="1472211" cy="19865"/>
+          <a:off x="1409575" y="1090761"/>
+          <a:ext cx="1057954" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4324,10 +5088,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1472211" y="9932"/>
+                <a:pt x="1057954" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4386,8 +5150,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1951257" y="1489012"/>
-        <a:ext cx="73610" cy="73610"/>
+        <a:off x="1912103" y="1071501"/>
+        <a:ext cx="52897" cy="52897"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -4397,8 +5161,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2185394" y="569989"/>
-          <a:ext cx="986660" cy="493330"/>
+          <a:off x="2080358" y="411077"/>
+          <a:ext cx="709030" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4473,8 +5237,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2199843" y="584438"/>
-        <a:ext cx="957762" cy="464432"/>
+        <a:off x="2090741" y="421460"/>
+        <a:ext cx="688264" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -4484,8 +5248,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3172055" y="806721"/>
-          <a:ext cx="394664" cy="19865"/>
+          <a:off x="2789389" y="581145"/>
+          <a:ext cx="283612" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4496,10 +5260,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="394664" y="9932"/>
+                <a:pt x="283612" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4558,8 +5322,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3359521" y="806788"/>
-        <a:ext cx="19733" cy="19733"/>
+        <a:off x="2924104" y="581244"/>
+        <a:ext cx="14180" cy="14180"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -4569,8 +5333,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="569989"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="411077"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4693,8 +5457,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="584438"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="421460"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -4704,8 +5468,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="1519033" y="1799549"/>
-          <a:ext cx="938057" cy="19865"/>
+          <a:off x="1601500" y="1294607"/>
+          <a:ext cx="674103" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4716,10 +5480,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="938057" y="9932"/>
+                <a:pt x="674103" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4778,8 +5542,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1964610" y="1786031"/>
-        <a:ext cx="46902" cy="46902"/>
+        <a:off x="1921700" y="1284944"/>
+        <a:ext cx="33705" cy="33705"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -4789,8 +5553,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2185394" y="1137319"/>
-          <a:ext cx="986660" cy="493330"/>
+          <a:off x="2080358" y="818769"/>
+          <a:ext cx="709030" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4881,8 +5645,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2199843" y="1151768"/>
-        <a:ext cx="957762" cy="464432"/>
+        <a:off x="2090741" y="829152"/>
+        <a:ext cx="688264" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -4892,8 +5656,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3172055" y="1374052"/>
-          <a:ext cx="394664" cy="19865"/>
+          <a:off x="2789389" y="988838"/>
+          <a:ext cx="283612" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4904,10 +5668,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="394664" y="9932"/>
+                <a:pt x="283612" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4966,8 +5730,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3359521" y="1374118"/>
-        <a:ext cx="19733" cy="19733"/>
+        <a:off x="2924104" y="988937"/>
+        <a:ext cx="14180" cy="14180"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -4977,8 +5741,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="1137319"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="818769"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5101,8 +5865,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="1151768"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="829152"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -5112,8 +5876,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="1642510" y="2508712"/>
-          <a:ext cx="691103" cy="19865"/>
+          <a:off x="1690233" y="1804223"/>
+          <a:ext cx="496637" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5124,10 +5888,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="691103" y="9932"/>
+                <a:pt x="496637" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5186,8 +5950,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1970784" y="2501367"/>
-        <a:ext cx="34555" cy="34555"/>
+        <a:off x="1926136" y="1798996"/>
+        <a:ext cx="24831" cy="24831"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -5197,8 +5961,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2185394" y="2555644"/>
-          <a:ext cx="986660" cy="493330"/>
+          <a:off x="2080358" y="1838001"/>
+          <a:ext cx="709030" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5273,8 +6037,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2199843" y="2570093"/>
-        <a:ext cx="957762" cy="464432"/>
+        <a:off x="2090741" y="1848384"/>
+        <a:ext cx="688264" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -5284,8 +6048,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2900358" y="2366879"/>
-          <a:ext cx="938057" cy="19865"/>
+          <a:off x="2594143" y="1702300"/>
+          <a:ext cx="674103" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5296,10 +6060,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="938057" y="9932"/>
+                <a:pt x="674103" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5358,8 +6122,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3345936" y="2353361"/>
-        <a:ext cx="46902" cy="46902"/>
+        <a:off x="2914342" y="1692636"/>
+        <a:ext cx="33705" cy="33705"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -5369,8 +6133,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="1704649"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="1226462"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5461,8 +6225,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="1719098"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="1236845"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -5472,8 +6236,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3126372" y="2650544"/>
-          <a:ext cx="486030" cy="19865"/>
+          <a:off x="2756560" y="1906146"/>
+          <a:ext cx="349269" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5484,10 +6248,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="486030" y="9932"/>
+                <a:pt x="349269" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5546,8 +6310,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3357236" y="2648326"/>
-        <a:ext cx="24301" cy="24301"/>
+        <a:off x="2922463" y="1904603"/>
+        <a:ext cx="17463" cy="17463"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -5557,8 +6321,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="2271979"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="1634154"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5649,8 +6413,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="2286428"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="1644537"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -5660,8 +6424,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3126372" y="2934209"/>
-          <a:ext cx="486030" cy="19865"/>
+          <a:off x="2756560" y="2109992"/>
+          <a:ext cx="349269" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5672,10 +6436,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="486030" y="9932"/>
+                <a:pt x="349269" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5734,8 +6498,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3357236" y="2931991"/>
-        <a:ext cx="24301" cy="24301"/>
+        <a:off x="2922463" y="2108450"/>
+        <a:ext cx="17463" cy="17463"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -5745,8 +6509,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="2839309"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="2041847"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5837,8 +6601,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="2853758"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="2052230"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -5848,8 +6612,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="2900358" y="3217874"/>
-          <a:ext cx="938057" cy="19865"/>
+          <a:off x="2594143" y="2313839"/>
+          <a:ext cx="674103" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5860,10 +6624,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="938057" y="9932"/>
+                <a:pt x="674103" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5922,8 +6686,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3345936" y="3204356"/>
-        <a:ext cx="46902" cy="46902"/>
+        <a:off x="2914342" y="2304175"/>
+        <a:ext cx="33705" cy="33705"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -5933,8 +6697,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="3406639"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="2449539"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6025,8 +6789,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="3421088"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="2459922"/>
+        <a:ext cx="2200881" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -6036,8 +6800,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="975814" y="3217874"/>
-          <a:ext cx="2024496" cy="19865"/>
+          <a:off x="1211134" y="2313839"/>
+          <a:ext cx="1454835" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6048,10 +6812,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="2024496" y="9932"/>
+                <a:pt x="1454835" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6106,8 +6870,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1937449" y="3177195"/>
-        <a:ext cx="101224" cy="101224"/>
+        <a:off x="1902181" y="2284657"/>
+        <a:ext cx="72741" cy="72741"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -6117,8 +6881,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2185394" y="3973969"/>
-          <a:ext cx="986660" cy="493330"/>
+          <a:off x="2080358" y="2857232"/>
+          <a:ext cx="709030" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6193,8 +6957,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2199843" y="3988418"/>
-        <a:ext cx="957762" cy="464432"/>
+        <a:off x="2090741" y="2867615"/>
+        <a:ext cx="688264" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -6204,8 +6968,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3172055" y="4210702"/>
-          <a:ext cx="394664" cy="19865"/>
+          <a:off x="2789389" y="3027300"/>
+          <a:ext cx="283612" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6216,10 +6980,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="9932"/>
+                <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="394664" y="9932"/>
+                <a:pt x="283612" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6274,8 +7038,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3359521" y="4210768"/>
-        <a:ext cx="19733" cy="19733"/>
+        <a:off x="2924104" y="3027399"/>
+        <a:ext cx="14180" cy="14180"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -6285,8 +7049,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3566719" y="3973969"/>
-          <a:ext cx="3091563" cy="493330"/>
+          <a:off x="3073001" y="2857232"/>
+          <a:ext cx="2221647" cy="354515"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6393,8 +7157,1230 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3581168" y="3988418"/>
-        <a:ext cx="3062665" cy="464432"/>
+        <a:off x="3083384" y="2867615"/>
+        <a:ext cx="2200881" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="581149" y="3672617"/>
+          <a:ext cx="1112397" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Profile(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>고객 정보</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="591532" y="3683000"/>
+        <a:ext cx="1091631" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="18752467">
+          <a:off x="1603939" y="3638839"/>
+          <a:ext cx="553334" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="553334" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1866773" y="3632195"/>
+        <a:ext cx="27666" cy="27666"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2067667" y="3264924"/>
+          <a:ext cx="709030" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>성별</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2078050" y="3275307"/>
+        <a:ext cx="688264" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2776697" y="3434993"/>
+          <a:ext cx="288355" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="288355" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2913666" y="3434973"/>
+        <a:ext cx="14417" cy="14417"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3065053" y="3264924"/>
+          <a:ext cx="2221200" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>여성이면 남성보다 완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3075436" y="3275307"/>
+        <a:ext cx="2200434" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="1693547" y="3842685"/>
+          <a:ext cx="374119" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="374119" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1871254" y="3840521"/>
+        <a:ext cx="18705" cy="18705"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2067667" y="3672617"/>
+          <a:ext cx="709030" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2078050" y="3683000"/>
+        <a:ext cx="688264" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2776697" y="3842685"/>
+          <a:ext cx="288355" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="288355" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2913666" y="3842666"/>
+        <a:ext cx="14417" cy="14417"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3065053" y="3672617"/>
+          <a:ext cx="2221200" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득이 높으면</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>만불</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>+) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3075436" y="3683000"/>
+        <a:ext cx="2200434" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="2847533">
+          <a:off x="1603939" y="4046532"/>
+          <a:ext cx="553334" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="553334" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="1866773" y="4039887"/>
+        <a:ext cx="27666" cy="27666"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2067667" y="4080309"/>
+          <a:ext cx="709030" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>나이</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2078050" y="4090692"/>
+        <a:ext cx="688264" cy="333749"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2776697" y="4250378"/>
+          <a:ext cx="297877" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="297877" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2918189" y="4250120"/>
+        <a:ext cx="14893" cy="14893"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3074575" y="4080309"/>
+          <a:ext cx="2221200" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="5B9BD5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>나이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(54) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은면 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3084958" y="4090692"/>
+        <a:ext cx="2200434" cy="333749"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -7760,13 +9746,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>234462</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -9178,9 +11164,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B68908F-2BBD-42FC-9E49-502A762C6F8E}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_2/project2_project status(C2)xlsx.xlsx
+++ b/project_2/project2_project status(C2)xlsx.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100AD062-9B8D-476D-9705-B9515056855D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B5C75D-AF26-46AF-BC40-CEF79F2B3CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="319">
   <si>
     <t>reward</t>
   </si>
@@ -69,49 +69,46 @@
     <t>event</t>
   </si>
   <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>object</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dataset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portfolio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profile</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transcript</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>value</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>object</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>str</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dataset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>portfolio</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>profile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transcript</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -123,10 +120,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>columns</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,14 +165,6 @@
   </si>
   <si>
     <t>경과 시간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>실험 시작 시점부터 흐른 시간(단위: 시간/hour)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이벤트 종류에 따라 내용이 다름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -274,9 +259,6 @@
     </r>
   </si>
   <si>
-    <t>1단계 — 문제 정의 (가설 트리)</t>
-  </si>
-  <si>
     <t>주어진 이슈(또는 도메인 데이터셋)를 가설 트리로 구조화한다.</t>
   </si>
   <si>
@@ -347,9 +329,6 @@
     <t>H1·H2·H3가 신규·유지·객단가로 매출의 세 축을 빠짐없이 덮는다.</t>
   </si>
   <si>
-    <t>2단계 — 지표 지도 그리기 (AARRR 등)</t>
-  </si>
-  <si>
     <t>가설 트리의 각 가지를 AARRR 어느 단계 지표로 측정할지 매핑한다. HEART, GAME 등 다른 지표 설계 프레임워크를 적용할 수 있다.</t>
   </si>
   <si>
@@ -386,9 +365,6 @@
       </rPr>
       <t>: 가설-지표 매핑표 (가설 / AARRR 단계 / 측정 지표 / 데이터 소스 / 측정 가능 여부)</t>
     </r>
-  </si>
-  <si>
-    <t>3단계 — 원인 분해 (로직 트리 · 이슈 트리)</t>
   </si>
   <si>
     <t>2단계에서 좁혀진 문제 지점을 로직 트리로 재분해한다.</t>
@@ -599,9 +575,6 @@
   </si>
   <si>
     <t>경쟁사 전환(H2-3) 같은 가지는 대부분의 공개 데이터로 검증할 수 없다. 넣는 것 자체는 옳다. 다만 2단계 매핑표에서 “측정 불가”로 표시하고, 결론에서 “이 원인은 배제하지 못했다”고 밝혀야 한다. 슬쩍 지우는 것이 가장 나쁜 처리다.</t>
-  </si>
-  <si>
-    <t>4단계 — 통계적 검증</t>
   </si>
   <si>
     <t>각 가설을 적절한 통계 기법으로 검증한다.</t>
@@ -943,7 +916,532 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>North Star Metric</t>
+    <t>오퍼가 정말 손님을 움직이고 있을까</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오퍼 발송 전략을 세그먼트·오퍼 설계 관점에서 최적화하면,
+같은 예산으로 더 높은 반응률과 더 낮은 낭비율을 만들 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AARRR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1단계 — 문제 정의 (가설 트리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2단계 — 지표 지도 그리기 (AARRR 등)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3단계 — 원인 분해 (로직 트리 · 이슈 트리)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4단계 — 통계적 검증</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채택 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Starbucks Rewards App Data의 경우 기 가입되어 있는 멤버들의 프로모션 반응에 해당하여 Acquisition이나 Referral에 대한 정보가 없고 Retention의 경우에도 해당 데이터의 기간이 30일로 제한적이라 사용에 제한이 있는 것으로 확인됨.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로모션의 전체 완료율만 확인하면 성과가 낮은 이유를 구분하기 어렵다.
+고객이 프로모션을 확인하지 않은 것인지, 확인했지만 조건을 달성하지 않은 것인지에 따라 개선 방법이 달라진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>어떤 고객군·프로모션 조합에서 수신 후 열람 또는 열람 후 완료의 병목이 발생하며, 무엇을 우선 개선해야 하는가?</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tier A — 지금 쓸 수 있는 실전 지표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 완료율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오퍼 1건당 매출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순증 전환율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P(구매 | 노출) - P(구매 | 미노출)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1단계 가설 트리의 두 갈래를 그대로 퍼널 절단 기준으로 씁니다. 노출율·조건부전환율·전체완료율 세 지표 모두 이 두 축으로 나눠 봅니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offer type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward (평균 4.2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duration (평균 6.7일)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Difficulty (평균 7.7)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍼널 3단계 전체에 적용 → 어떤 오퍼 속성이 어느 단계에서 이탈을 만드는지 분리해서 봄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Channels
+web·email·mobile·social</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성별</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소득(8만불 기준)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이 (평균 54세 기준)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퍼널 3단계 전체에 적용 → 어떤 고객군이 어느 단계에서 이탈하는지 분리해서 봄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01 북극성 지표: Tier A로 시작할지, 처음부터 Tier B(순증)로 갈지
+Tier A는 3~4단계로 바로 진입 가능하지만 함정을 안고 감. Tier B는 정확하지만 대조군/시점비교 설계가 먼저 필요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02 informational 오퍼의 "전환" 정의
+completed 이벤트가 없는 오퍼 타입을 노출 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 노출 단계에서 끊고 별도로 다룰지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실험 시작 시점부터 흐른 시간
+(단위: 시간/hour)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. profile의 성별, 소득 정보가 Null인 2,175명의 경우 나이가 118세로 임의의 값이 입력된 것으로 추측
+2. profile 관련 분석 시 2,175명은 제외함.
+3. portfolio informational offer의 경우 completed가 집계되지 않음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,175명 Null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,175명 118로 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Portfolio: id와 mapping
+이벤트 종류에 따라 내용이 다름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profile: id와 mapping</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>r</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신 후 유효기간 내 완료된 offer(bogo, discount) 수
+÷ 발송된 offer(bogo, discount) 수 × 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발송 → 수신 → 완료의 단일 퍼널에 해당</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transcript.json의 evnet 3종(offer received → offer viewed → offer completed)을 그대로 funnel 단계로 매핑
+informational offer는 reward·difficulty가 0이라 completed event 자체가 없어, 별도 경로로 갈라짐
+received → viewed → completed 3단계 funnel. informational offer는 completed event가 없어 viewed 후 transaction을 대리 지표로 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offer 설계 축
+Offer(프로모션) 설계에 따라 완료율 차이가 있는가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profile 속성 축
+Profile(고객 정보)에 따라 완료율이 다를 것이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설</t>
+  </si>
+  <si>
+    <t>Activation</t>
+  </si>
+  <si>
+    <t>transcript.json</t>
+  </si>
+  <si>
+    <t>가능</t>
+  </si>
+  <si>
+    <t>Retention</t>
+  </si>
+  <si>
+    <t>transcript.json (transaction, offer received)</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>profile.json + transcript.json</t>
+  </si>
+  <si>
+    <t>portfolio.json + transcript.json</t>
+  </si>
+  <si>
+    <t>AARRR 단계</t>
+  </si>
+  <si>
+    <t>측정 지표</t>
+  </si>
+  <si>
+    <t>데이터 소스</t>
+  </si>
+  <si>
+    <t>측정 가능 여부</t>
+  </si>
+  <si>
+    <t>열람 후 완료 → 오퍼가 실제로 구매를 유도한 것이다</t>
+  </si>
+  <si>
+    <t>오퍼 열람율, 열람→완료 전환율</t>
+  </si>
+  <si>
+    <t>무열람 완료 → 오퍼 없이도 샀을 고객(Sure-thing)일 것이다</t>
+  </si>
+  <si>
+    <t>Sure-thing 비율</t>
+  </si>
+  <si>
+    <t>오퍼를 받으면 재구매 텀이 짧아질 것이다</t>
+  </si>
+  <si>
+    <t>오퍼타입별 구매텀 단축률</t>
+  </si>
+  <si>
+    <t>가능 (신규)</t>
+  </si>
+  <si>
+    <t>소득이 높으면 완료율이 높을 것이다</t>
+  </si>
+  <si>
+    <t>세그먼트별 완료율, ARPU</t>
+  </si>
+  <si>
+    <t>여성이면 완료율이 높을 것이다</t>
+  </si>
+  <si>
+    <t>성별 완료율, 성별 평균 거래액</t>
+  </si>
+  <si>
+    <t>할인형이 BOGO보다 완료율이 높을 것이다</t>
+  </si>
+  <si>
+    <t>오퍼유형별 완료율, 리워드 대비 ROI</t>
+  </si>
+  <si>
+    <t>오퍼타입별로 객단가가 다를 것이다</t>
+  </si>
+  <si>
+    <t>오퍼타입별 평균 거래액</t>
+  </si>
+  <si>
+    <t>리워드 허들이 낮으면 완료율이 높을 것이다</t>
+  </si>
+  <si>
+    <t>난이도 구간별 완료율(회귀계수)</t>
+  </si>
+  <si>
+    <t>가능(미실행)</t>
+  </si>
+  <si>
+    <t>Acquisition</t>
+  </si>
+  <si>
+    <t>Referral</t>
+  </si>
+  <si>
+    <t>가입 경로(광고/추천/오가닉) 정보 없음, became_member_on만 존재</t>
+  </si>
+  <si>
+    <t>유입 채널, UTM/캠페인 태그, 다운로드 소스</t>
+  </si>
+  <si>
+    <t>추천·초대·공유 관련 필드가 데이터셋에 전무</t>
+  </si>
+  <si>
+    <t>추천인 코드, 초대 발송/수락 로그, 소셜 공유 이벤트</t>
+  </si>
+  <si>
+    <t>측정 불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Retention의 한계: Sure-thing 비율과 구매텀 단축률 모두 30일 관찰기간 안에서 잰 근사치입니다. 진짜 이탈(churn) 여부는 이 데이터로 볼 수 없습니다.</t>
+  </si>
+  <si>
+    <t>동일 고객이 같은 프로모션을 여러 번 받을 수 있으므로 고객·프로모션·수신 시점을 기준으로 각 프로모션 수신 건을 구분해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>열람과 완료는 해당 프로모션의 수신 이후이면서 유효기간 안에 발생한 경우만 연결해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정보 제공형 프로모션은 완료 조건이 없으므로 열람률까지만 평가한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>여러 채널이 하나의 프로모션에 함께 포함되어 있어 개별 채널의 독립적인 효과를 확정하기 어렵다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채널 분석은 채널의 인과효과가 아니라 채널 포함 여부 또는 채널 조합과 성과의 연관성으로 해석한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객정보가 누락되고 나이가 118세로 기록된 2,175명은 고객 특성별 분석에서 별도로 처리한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제 기록에는 프로모션 ID가 없으므로 특정 결제를 특정 프로모션의 성과로 직접 귀속할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로모션 설계는 10개뿐이므로 보상·기간·난이도·채널 각각의 독립적인 효과를 강하게 단정하지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+      </rPr>
+      <t>Σ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>전환매출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>발송건수</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05. AARRR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04. 다음 결정이 필요한 지점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01. 북극성 지표 후보</t>
+  </si>
+  <si>
+    <t>02. 오퍼 반응 퍼널</t>
+  </si>
+  <si>
+    <t>03. 세그먼트 축 — 퍼널의 모든 단계를 가르는 절단면</t>
+  </si>
+  <si>
+    <t>6. 현재 측정하기 어려운 지표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지표</t>
+  </si>
+  <si>
+    <t>측정이 어려운 이유</t>
+  </si>
+  <si>
+    <t>추가로 필요한 데이터</t>
+  </si>
+  <si>
+    <t>개별 채널의 직접 효과</t>
+  </si>
+  <si>
+    <t>실제로 어떤 채널에서 열람했는지 알 수 없음</t>
+  </si>
+  <si>
+    <t>채널별 노출·클릭 로그</t>
+  </si>
+  <si>
+    <t>프로모션의 정확한 구매 유발 효과</t>
+  </si>
+  <si>
+    <t>결제 기록에 프로모션 ID가 없음</t>
+  </si>
+  <si>
+    <t>결제별 프로모션 연결 정보 또는 대조군</t>
+  </si>
+  <si>
+    <t>정확한 ROI</t>
+  </si>
+  <si>
+    <t>프로모션 운영비와 상품 원가 정보가 없음</t>
+  </si>
+  <si>
+    <t>캠페인 비용·상품 원가·마진 데이터</t>
+  </si>
+  <si>
+    <t>장기 재구매 효과</t>
+  </si>
+  <si>
+    <t>관찰기간이 약 30일로 짧음</t>
+  </si>
+  <si>
+    <t>장기간 고객 행동 기록</t>
+  </si>
+  <si>
+    <t>7. 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신 후 완료율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tier B — 사용 불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간 내 완료된 offer(bogo, discount) 수
+÷ 발송된 offer(bogo, discount) 수 × 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신된 offer(bogo, discount) 수
+÷ 발송된 offer(bogo, discount) 수 × 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction의 amount 합계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시철, 서영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -951,10 +1449,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+    <numFmt numFmtId="184" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1054,8 +1553,91 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Wingdings 3"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="161"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1086,8 +1668,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1280,13 +1868,77 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1307,9 +1959,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1386,9 +2035,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1401,6 +2047,12 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1408,15 +2060,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1428,18 +2071,139 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2234,7 +2998,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2242,7 +3006,7 @@
             <a:t>Offer(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2250,7 +3014,7 @@
             <a:t>행사</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2258,14 +3022,14 @@
             <a:t>) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2281,7 +3045,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2297,7 +3061,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2321,14 +3085,14 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Offer type</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2344,7 +3108,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2360,7 +3124,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2384,14 +3148,14 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Reward</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2407,7 +3171,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2423,7 +3187,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2447,7 +3211,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2455,7 +3219,7 @@
             <a:t>Reward</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2463,7 +3227,7 @@
             <a:t>가 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2471,7 +3235,7 @@
             <a:t>(4.2)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2479,7 +3243,7 @@
             <a:t> 보다 높은 경우</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2487,7 +3251,7 @@
             <a:t>,</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2495,14 +3259,14 @@
             <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2518,7 +3282,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2534,7 +3298,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2558,7 +3322,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2566,7 +3330,7 @@
             <a:t>완료율은 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2574,7 +3338,7 @@
             <a:t>discount &gt; bogo &gt; information </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2582,14 +3346,14 @@
             <a:t>순으로 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2605,7 +3369,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2621,7 +3385,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2645,7 +3409,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2653,7 +3417,7 @@
             <a:t>Duration(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2661,14 +3425,14 @@
             <a:t>기간</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>)</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2684,7 +3448,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2700,7 +3464,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2724,7 +3488,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2732,7 +3496,7 @@
             <a:t>Duration</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2740,7 +3504,7 @@
             <a:t>이 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2748,7 +3512,7 @@
             <a:t>(6.7)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2756,7 +3520,7 @@
             <a:t>보다 높은 경우</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2764,7 +3528,7 @@
             <a:t>, </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2772,14 +3536,14 @@
             <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2795,7 +3559,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2811,7 +3575,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2835,14 +3599,14 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Channels</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2858,7 +3622,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2874,7 +3638,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2898,7 +3662,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2906,7 +3670,7 @@
             <a:t>Web</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2914,14 +3678,14 @@
             <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2937,7 +3701,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2953,7 +3717,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -2977,7 +3741,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2985,7 +3749,7 @@
             <a:t>Mobile</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -2993,14 +3757,14 @@
             <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3016,7 +3780,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3032,7 +3796,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3056,7 +3820,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3064,7 +3828,7 @@
             <a:t>Social</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3072,14 +3836,14 @@
             <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3095,7 +3859,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3111,7 +3875,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3135,7 +3899,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3143,7 +3907,7 @@
             <a:t>email</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3151,14 +3915,14 @@
             <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3174,7 +3938,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3190,7 +3954,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3214,14 +3978,14 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Difficulty</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3237,7 +4001,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3249,7 +4013,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3269,7 +4033,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3277,7 +4041,7 @@
             <a:t>Difficulty</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3285,7 +4049,7 @@
             <a:t>가 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3293,7 +4057,7 @@
             <a:t>(7.7) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3301,14 +4065,14 @@
             <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3324,7 +4088,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3336,7 +4100,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3356,7 +4120,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3367,7 +4131,7 @@
             <a:t>Profile(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3378,7 +4142,7 @@
             <a:t>고객 정보</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3389,7 +4153,7 @@
             <a:t>)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3400,7 +4164,7 @@
             <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3410,7 +4174,7 @@
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3429,7 +4193,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3441,7 +4205,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3461,7 +4225,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3475,14 +4239,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" type="parTrans" cxnId="{9457F039-2CF0-400D-9C71-03F7FA015A09}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3494,7 +4258,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3514,7 +4278,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3528,14 +4292,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" type="parTrans" cxnId="{415577E8-A702-41BC-965B-528E316FA7F6}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3547,7 +4311,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3567,7 +4331,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3581,14 +4345,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" type="parTrans" cxnId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3600,7 +4364,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3620,7 +4384,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3631,7 +4395,7 @@
             <a:t>소득이 높으면</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3642,7 +4406,7 @@
             <a:t>(8</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3653,7 +4417,7 @@
             <a:t>만불</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3664,7 +4428,7 @@
             <a:t>+) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3678,14 +4442,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" type="parTrans" cxnId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3697,7 +4461,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3719,7 +4483,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3733,14 +4497,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" type="parTrans" cxnId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3752,7 +4516,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3785,7 +4549,7 @@
         <a:p>
           <a:pPr latinLnBrk="1"/>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3793,7 +4557,7 @@
             <a:t>나이 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3801,7 +4565,7 @@
             <a:t>(54) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3809,7 +4573,7 @@
             <a:t>보다 높은면 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3820,7 +4584,7 @@
             <a:t>완료율이</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -3828,14 +4592,14 @@
             <a:t> 낮을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -3844,14 +4608,14 @@
       </dgm:t>
     </dgm:pt>
     <dgm:pt modelId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" type="parTrans" cxnId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}">
-      <dgm:prSet/>
+      <dgm:prSet custT="1"/>
       <dgm:spPr/>
       <dgm:t>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3863,7 +4627,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr latinLnBrk="1"/>
-          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
         </a:p>
       </dgm:t>
     </dgm:pt>
@@ -3884,7 +4648,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" type="pres">
-      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="2" custScaleX="156668">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="2" custScaleX="201190">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3908,7 +4672,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" type="pres">
-      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="8">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="8" custScaleX="120714">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3932,7 +4696,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" type="pres">
-      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="11" custScaleX="313336" custLinFactNeighborX="-620">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-620">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3956,7 +4720,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" type="pres">
-      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="8">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="8" custScaleX="120714">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -3980,7 +4744,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" type="pres">
-      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4004,7 +4768,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" type="pres">
-      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="8">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="8" custScaleX="120714">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4028,7 +4792,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" type="pres">
-      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4052,7 +4816,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}" type="pres">
-      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="8">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="8" custScaleX="120714">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4076,7 +4840,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" type="pres">
-      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4100,7 +4864,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{2D542640-C237-42B5-8470-73084719F8F3}" type="pres">
-      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4124,7 +4888,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}" type="pres">
-      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4148,7 +4912,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{220D319D-36C0-42A0-A946-F197C4269C14}" type="pres">
-      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4172,7 +4936,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" type="pres">
-      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="8">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="8" custScaleX="120714">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4196,7 +4960,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" type="pres">
-      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="11" custScaleX="313336">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4212,7 +4976,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" type="pres">
-      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="1" presStyleCnt="2" custScaleX="156890" custLinFactNeighborX="-14777">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="1" presStyleCnt="2" custScaleX="201190" custLinFactNeighborX="-14777">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4236,7 +5000,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" type="pres">
-      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="5" presStyleCnt="8" custLinFactNeighborX="-2012">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="5" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4260,7 +5024,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" type="pres">
-      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="8" presStyleCnt="11" custScaleX="313273" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="8" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4284,7 +5048,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" type="pres">
-      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="6" presStyleCnt="8" custLinFactNeighborX="-2012">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="6" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4308,7 +5072,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" type="pres">
-      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="9" presStyleCnt="11" custScaleX="313273" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="9" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4332,7 +5096,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" type="pres">
-      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="7" presStyleCnt="8" custLinFactNeighborX="-2012">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="7" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4356,7 +5120,7 @@
       <dgm:spPr/>
     </dgm:pt>
     <dgm:pt modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" type="pres">
-      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="10" presStyleCnt="11" custScaleX="313273">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="10" presStyleCnt="11" custScaleX="523095">
         <dgm:presLayoutVars>
           <dgm:chPref val="3"/>
         </dgm:presLayoutVars>
@@ -4570,7 +5334,13 @@
       </a:schemeClr>
     </a:solidFill>
   </dgm:bg>
-  <dgm:whole/>
+  <dgm:whole>
+    <a:ln>
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </dgm:whole>
   <dgm:extLst>
     <a:ext uri="http://schemas.microsoft.com/office/drawing/2008/diagram">
       <dsp:dataModelExt xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" relId="rId5" minVer="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
@@ -4597,8 +5367,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="685922" y="1430308"/>
-          <a:ext cx="1110823" cy="354515"/>
+          <a:off x="370660" y="1805623"/>
+          <a:ext cx="1800813" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4640,12 +5410,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4658,7 +5428,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -4666,7 +5436,7 @@
             <a:t>Offer(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -4674,7 +5444,7 @@
             <a:t>행사</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" i="0" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -4682,14 +5452,14 @@
             <a:t>) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" i="0" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -4697,8 +5467,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="696305" y="1440691"/>
-        <a:ext cx="1090057" cy="333749"/>
+        <a:off x="383768" y="1818731"/>
+        <a:ext cx="1774597" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -4708,8 +5478,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1211134" y="886915"/>
-          <a:ext cx="1454835" cy="14378"/>
+          <a:off x="1432196" y="1121529"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4723,7 +5493,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1454835" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4762,7 +5532,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4774,7 +5544,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -4782,8 +5552,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1902181" y="857733"/>
-        <a:ext cx="72741" cy="72741"/>
+        <a:off x="2304575" y="1082803"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -4793,8 +5563,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2080358" y="3384"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2529506" y="4273"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -4836,12 +5606,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4854,14 +5624,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Offer type</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -4869,8 +5639,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2090741" y="13767"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2542614" y="17381"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -4880,8 +5650,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2789389" y="173453"/>
-          <a:ext cx="279216" cy="14378"/>
+          <a:off x="3609994" y="220854"/>
+          <a:ext cx="352482" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -4895,7 +5665,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="279216" y="7189"/>
+                <a:pt x="352482" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -4934,7 +5704,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -4946,7 +5716,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -4954,8 +5724,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922016" y="173662"/>
-        <a:ext cx="13960" cy="13960"/>
+        <a:off x="3777423" y="219231"/>
+        <a:ext cx="17624" cy="17624"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -4965,8 +5735,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3068605" y="3384"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3962476" y="4273"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5008,12 +5778,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5026,7 +5796,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5034,7 +5804,7 @@
             <a:t>완료율은 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5042,7 +5812,7 @@
             <a:t>discount &gt; bogo &gt; information </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5050,14 +5820,14 @@
             <a:t>순으로 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5065,8 +5835,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3078988" y="13767"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3975584" y="17381"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -5076,8 +5846,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1409575" y="1090761"/>
-          <a:ext cx="1057954" cy="14378"/>
+          <a:off x="1682708" y="1378865"/>
+          <a:ext cx="1335563" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5091,7 +5861,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1057954" y="7189"/>
+                <a:pt x="1335563" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5130,7 +5900,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5142,7 +5912,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5150,8 +5920,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1912103" y="1071501"/>
-        <a:ext cx="52897" cy="52897"/>
+        <a:off x="2317100" y="1352664"/>
+        <a:ext cx="66778" cy="66778"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -5161,8 +5931,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2080358" y="411077"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2529506" y="518944"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5204,12 +5974,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5222,14 +5992,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Reward</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5237,8 +6007,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2090741" y="421460"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2542614" y="532052"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -5248,8 +6018,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2789389" y="581145"/>
-          <a:ext cx="283612" cy="14378"/>
+          <a:off x="3609994" y="735525"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5263,7 +6033,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="283612" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5302,7 +6072,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5314,7 +6084,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5322,8 +6092,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2924104" y="581244"/>
-        <a:ext cx="14180" cy="14180"/>
+        <a:off x="3780059" y="733763"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -5333,8 +6103,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="411077"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="518944"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5376,12 +6146,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5394,7 +6164,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5402,7 +6172,7 @@
             <a:t>Reward</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5410,7 +6180,7 @@
             <a:t>가 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5418,7 +6188,7 @@
             <a:t>(4.2)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5426,7 +6196,7 @@
             <a:t> 보다 높은 경우</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5434,7 +6204,7 @@
             <a:t>,</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5442,14 +6212,14 @@
             <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5457,8 +6227,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="421460"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="532052"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -5468,8 +6238,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="1601500" y="1294607"/>
-          <a:ext cx="674103" cy="14378"/>
+          <a:off x="1924995" y="1636200"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5483,7 +6253,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="674103" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5522,7 +6292,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5534,7 +6304,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5542,8 +6312,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1921700" y="1284944"/>
-        <a:ext cx="33705" cy="33705"/>
+        <a:off x="2329215" y="1622115"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -5553,8 +6323,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2080358" y="818769"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2529506" y="1033615"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5596,12 +6366,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5614,7 +6384,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5622,7 +6392,7 @@
             <a:t>Duration(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5630,14 +6400,14 @@
             <a:t>기간</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>)</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5645,8 +6415,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2090741" y="829152"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2542614" y="1046723"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -5656,8 +6426,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2789389" y="988838"/>
-          <a:ext cx="283612" cy="14378"/>
+          <a:off x="3609994" y="1250197"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5671,7 +6441,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="283612" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5710,7 +6480,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5722,7 +6492,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5730,8 +6500,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2924104" y="988937"/>
-        <a:ext cx="14180" cy="14180"/>
+        <a:off x="3780059" y="1248435"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -5741,8 +6511,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="818769"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="1033615"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -5784,12 +6554,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5802,7 +6572,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5810,7 +6580,7 @@
             <a:t>Duration</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5818,7 +6588,7 @@
             <a:t>이 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5826,7 +6596,7 @@
             <a:t>(6.7)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5834,7 +6604,7 @@
             <a:t>보다 높은 경우</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5842,7 +6612,7 @@
             <a:t>, </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -5850,14 +6620,14 @@
             <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5865,8 +6635,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="829152"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="1046723"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -5876,8 +6646,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="1690233" y="1804223"/>
-          <a:ext cx="496637" cy="14378"/>
+          <a:off x="2037012" y="2279540"/>
+          <a:ext cx="626956" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -5891,7 +6661,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="496637" y="7189"/>
+                <a:pt x="626956" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -5930,7 +6700,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -5942,7 +6712,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -5950,8 +6720,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1926136" y="1798996"/>
-        <a:ext cx="24831" cy="24831"/>
+        <a:off x="2334816" y="2271055"/>
+        <a:ext cx="31347" cy="31347"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -5961,8 +6731,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2080358" y="1838001"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2529506" y="2320294"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6004,12 +6774,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6022,14 +6792,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Channels</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6037,8 +6807,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2090741" y="1848384"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2542614" y="2333402"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -6048,8 +6818,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2594143" y="1702300"/>
-          <a:ext cx="674103" cy="14378"/>
+          <a:off x="3363515" y="2150872"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6063,7 +6833,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="674103" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6102,7 +6872,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6114,7 +6884,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6122,8 +6892,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914342" y="1692636"/>
-        <a:ext cx="33705" cy="33705"/>
+        <a:off x="3767735" y="2136786"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -6133,8 +6903,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="1226462"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="1548287"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6176,12 +6946,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6194,7 +6964,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6202,7 +6972,7 @@
             <a:t>Web</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6210,14 +6980,14 @@
             <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6225,8 +6995,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="1236845"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="1561395"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -6236,8 +7006,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="2756560" y="1906146"/>
-          <a:ext cx="349269" cy="14378"/>
+          <a:off x="3568551" y="2408207"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6251,7 +7021,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="349269" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6290,7 +7060,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6302,7 +7072,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6310,8 +7080,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922463" y="1904603"/>
-        <a:ext cx="17463" cy="17463"/>
+        <a:off x="3777987" y="2404373"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -6321,8 +7091,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="1634154"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="2062958"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6364,12 +7134,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6382,7 +7152,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6390,7 +7160,7 @@
             <a:t>email</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6398,14 +7168,14 @@
             <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6413,8 +7183,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="1644537"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="2076066"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -6424,8 +7194,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="2756560" y="2109992"/>
-          <a:ext cx="349269" cy="14378"/>
+          <a:off x="3568551" y="2665543"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6439,7 +7209,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="349269" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6478,7 +7248,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6490,7 +7260,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6498,8 +7268,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922463" y="2108450"/>
-        <a:ext cx="17463" cy="17463"/>
+        <a:off x="3777987" y="2661709"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -6509,8 +7279,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="2041847"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="2577630"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6552,12 +7322,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6570,7 +7340,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6578,7 +7348,7 @@
             <a:t>Mobile</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6586,14 +7356,14 @@
             <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6601,8 +7371,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="2052230"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="2590738"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -6612,8 +7382,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="2594143" y="2313839"/>
-          <a:ext cx="674103" cy="14378"/>
+          <a:off x="3363515" y="2922879"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6627,7 +7397,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="674103" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6666,7 +7436,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6678,7 +7448,7 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6686,8 +7456,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914342" y="2304175"/>
-        <a:ext cx="33705" cy="33705"/>
+        <a:off x="3767735" y="2908793"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -6697,8 +7467,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="2449539"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="3092301"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6740,12 +7510,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6758,7 +7528,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6766,7 +7536,7 @@
             <a:t>Social</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -6774,14 +7544,14 @@
             <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6789,8 +7559,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="2459922"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="3105409"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -6800,8 +7570,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1211134" y="2313839"/>
-          <a:ext cx="1454835" cy="14378"/>
+          <a:off x="1432196" y="2922879"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6815,7 +7585,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1454835" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -6854,7 +7624,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6866,12 +7636,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1902181" y="2284657"/>
-        <a:ext cx="72741" cy="72741"/>
+        <a:off x="2304575" y="2884153"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -6881,8 +7651,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2080358" y="2857232"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2529506" y="3606973"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -6924,12 +7694,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -6942,14 +7712,14 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>Difficulty</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -6957,8 +7727,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2090741" y="2867615"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2542614" y="3620081"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -6968,8 +7738,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2789389" y="3027300"/>
-          <a:ext cx="283612" cy="14378"/>
+          <a:off x="3609994" y="3823554"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -6983,7 +7753,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="283612" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -7022,7 +7792,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="266700" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7034,12 +7804,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="600" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2924104" y="3027399"/>
-        <a:ext cx="14180" cy="14180"/>
+        <a:off x="3780059" y="3821792"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -7049,8 +7819,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3073001" y="2857232"/>
-          <a:ext cx="2221647" cy="354515"/>
+          <a:off x="3968026" y="3606973"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7092,12 +7862,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7110,7 +7880,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7118,7 +7888,7 @@
             <a:t>Difficulty</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7126,7 +7896,7 @@
             <a:t>가 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7134,7 +7904,7 @@
             <a:t>(7.7) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7142,14 +7912,14 @@
             <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -7157,8 +7927,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3083384" y="2867615"/>
-        <a:ext cx="2200881" cy="333749"/>
+        <a:off x="3981134" y="3620081"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -7168,8 +7938,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="581149" y="3672617"/>
-          <a:ext cx="1112397" cy="354515"/>
+          <a:off x="238394" y="4636316"/>
+          <a:ext cx="1800813" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7211,12 +7981,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7229,7 +7999,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7240,7 +8010,7 @@
             <a:t>Profile(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7251,7 +8021,7 @@
             <a:t>고객 정보</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7262,7 +8032,7 @@
             <a:t>)</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7273,7 +8043,7 @@
             <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7283,7 +8053,7 @@
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -7294,8 +8064,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="591532" y="3683000"/>
-        <a:ext cx="1091631" cy="333749"/>
+        <a:off x="251502" y="4649424"/>
+        <a:ext cx="1774597" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -7305,8 +8075,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1603939" y="3638839"/>
-          <a:ext cx="553334" cy="14378"/>
+          <a:off x="1926087" y="4595561"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -7320,7 +8090,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="553334" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -7359,7 +8129,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7371,12 +8141,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1866773" y="3632195"/>
-        <a:ext cx="27666" cy="27666"/>
+        <a:off x="2257889" y="4585287"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -7386,8 +8156,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2067667" y="3264924"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2511497" y="4121644"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7429,12 +8199,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7447,7 +8217,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7460,8 +8230,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2078050" y="3275307"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2524605" y="4134752"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -7471,8 +8241,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2776697" y="3434993"/>
-          <a:ext cx="288355" cy="14378"/>
+          <a:off x="3591984" y="4338225"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -7486,7 +8256,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="288355" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -7525,7 +8295,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7537,12 +8307,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2913666" y="3434973"/>
-        <a:ext cx="14417" cy="14417"/>
+        <a:off x="3764894" y="4336314"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -7552,8 +8322,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3065053" y="3264924"/>
-          <a:ext cx="2221200" cy="354515"/>
+          <a:off x="3956005" y="4121644"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7595,12 +8365,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7613,7 +8383,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7626,8 +8396,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3075436" y="3275307"/>
-        <a:ext cx="2200434" cy="333749"/>
+        <a:off x="3969113" y="4134752"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -7637,8 +8407,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1693547" y="3842685"/>
-          <a:ext cx="374119" cy="14378"/>
+          <a:off x="2039207" y="4852897"/>
+          <a:ext cx="472289" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -7652,7 +8422,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="374119" y="7189"/>
+                <a:pt x="472289" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -7691,7 +8461,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7703,12 +8473,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1871254" y="3840521"/>
-        <a:ext cx="18705" cy="18705"/>
+        <a:off x="2263545" y="4848279"/>
+        <a:ext cx="23614" cy="23614"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -7718,8 +8488,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2067667" y="3672617"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2511497" y="4636316"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7761,12 +8531,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7779,7 +8549,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7792,8 +8562,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2078050" y="3683000"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2524605" y="4649424"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -7803,8 +8573,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2776697" y="3842685"/>
-          <a:ext cx="288355" cy="14378"/>
+          <a:off x="3591984" y="4852897"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -7818,7 +8588,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="288355" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -7857,7 +8627,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7869,12 +8639,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2913666" y="3842666"/>
-        <a:ext cx="14417" cy="14417"/>
+        <a:off x="3764894" y="4850985"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -7884,8 +8654,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3065053" y="3672617"/>
-          <a:ext cx="2221200" cy="354515"/>
+          <a:off x="3956005" y="4636316"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -7927,12 +8697,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -7945,7 +8715,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7956,7 +8726,7 @@
             <a:t>소득이 높으면</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7967,7 +8737,7 @@
             <a:t>(8</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7978,7 +8748,7 @@
             <a:t>만불</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -7989,7 +8759,7 @@
             <a:t>+) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8002,8 +8772,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3075436" y="3683000"/>
-        <a:ext cx="2200434" cy="333749"/>
+        <a:off x="3969113" y="4649424"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -8013,8 +8783,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1603939" y="4046532"/>
-          <a:ext cx="553334" cy="14378"/>
+          <a:off x="1926087" y="5110232"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -8028,7 +8798,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="553334" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -8067,7 +8837,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -8079,12 +8849,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1866773" y="4039887"/>
-        <a:ext cx="27666" cy="27666"/>
+        <a:off x="2257889" y="5099958"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -8094,8 +8864,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2067667" y="4080309"/>
-          <a:ext cx="709030" cy="354515"/>
+          <a:off x="2511497" y="5150987"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -8137,12 +8907,12 @@
         </a:fontRef>
       </dsp:style>
       <dsp:txBody>
-        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -8155,7 +8925,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8168,8 +8938,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2078050" y="4090692"/>
-        <a:ext cx="688264" cy="333749"/>
+        <a:off x="2524605" y="5164095"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -8179,8 +8949,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2776697" y="4250378"/>
-          <a:ext cx="297877" cy="14378"/>
+          <a:off x="3591984" y="5367568"/>
+          <a:ext cx="376041" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -8194,7 +8964,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297877" y="7189"/>
+                <a:pt x="376041" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -8233,7 +9003,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="222250" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -8245,12 +9015,12 @@
             </a:spcAft>
             <a:buNone/>
           </a:pPr>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="500" kern="1200"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2918189" y="4250120"/>
-        <a:ext cx="14893" cy="14893"/>
+        <a:off x="3770604" y="5365356"/>
+        <a:ext cx="18802" cy="18802"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -8260,8 +9030,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3074575" y="4080309"/>
-          <a:ext cx="2221200" cy="354515"/>
+          <a:off x="3968026" y="5150987"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -8308,7 +9078,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="311150" latinLnBrk="1">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
             <a:lnSpc>
               <a:spcPct val="90000"/>
             </a:lnSpc>
@@ -8321,7 +9091,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8329,7 +9099,7 @@
             <a:t>나이 평균</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8337,7 +9107,7 @@
             <a:t>(54) </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8345,7 +9115,7 @@
             <a:t>보다 높은면 </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8356,7 +9126,7 @@
             <a:t>완료율이</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
@@ -8364,14 +9134,14 @@
             <a:t> 낮을 것이다</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="700" b="1" kern="1200">
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
               <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
             <a:t>.</a:t>
           </a:r>
-          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="700" b="1" kern="1200">
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
             <a:solidFill>
               <a:sysClr val="windowText" lastClr="000000"/>
             </a:solidFill>
@@ -8379,8 +9149,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3084958" y="4090692"/>
-        <a:ext cx="2200434" cy="333749"/>
+        <a:off x="3981134" y="5164095"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -9746,15 +10516,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>440</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>4792980</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9777,6 +10547,55 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>24130</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>235</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4468209B-4015-4393-C8A5-C98718ECA0FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4161790"/>
+          <a:ext cx="8511540" cy="3062205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10079,613 +10898,616 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{464339BF-CD0E-4CF6-B158-81CFA6AF1918}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:C136"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.83203125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="32.9140625" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A3" s="21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A5" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A6" s="22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A8" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A3" s="22" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" s="20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" s="23" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A11" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A13" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" s="23" t="s">
+    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A15" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A8" s="22" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A16" s="24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" s="21" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A18" s="25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="21" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A19" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" s="21" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A20" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A21" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A22" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A23" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A25" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A26" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A27" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A28" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A30" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A31" s="20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" s="20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A36" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" s="23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A15" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A16" s="25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" s="26" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" s="26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" s="26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" s="26" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" s="26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" s="26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" s="26" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A43" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" s="20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A50" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A51" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52" s="26"/>
+      <c r="B52" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59" s="22" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60" s="24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" s="25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A70" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A71" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A72" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A73" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A74" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A75" s="25" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A77" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" s="26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" s="26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" s="26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" s="26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A30" s="23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" s="21" t="s">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A78" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A79" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A80" s="20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A82" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A83" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A84" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A85" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A86" s="20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A88" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" s="21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" s="21" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A36" s="22" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" s="21" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" s="23" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" s="21" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" s="23" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A43" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A44" s="21" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" s="21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" s="21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" s="23" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A50" s="24" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A51" s="24" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="27"/>
-      <c r="B52" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="23" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="26" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="26" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A65" s="26" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A66" s="26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A67" s="26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A68" s="26" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" s="26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A70" s="26" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A71" s="26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A72" s="26" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A73" s="26" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A74" s="26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A75" s="26" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A77" s="23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A78" s="21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="21" t="s">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A89" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A80" s="21" t="s">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A90" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A82" s="24" t="s">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A91" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A83" s="23" t="s">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A93" s="22" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A84" s="23" t="s">
+    <row r="95" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A95" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A85" s="23" t="s">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A96" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A97" s="20" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A86" s="21" t="s">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A98" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A88" s="22" t="s">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A100" s="22" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A89" s="21" t="s">
+    <row r="102" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A102" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A90" s="21" t="s">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A103" s="20" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A91" s="21" t="s">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A104" s="20" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A93" s="23" t="s">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A106" s="22" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A95" s="22" t="s">
+    <row r="108" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+      <c r="A108" s="21" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A96" s="21" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A97" s="21" t="s">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A110" s="20" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A98" s="21" t="s">
+    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.45">
+      <c r="A112" s="23" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A100" s="23" t="s">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A114" s="26" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A102" s="22" t="s">
+      <c r="B114" s="17" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A103" s="21" t="s">
+      <c r="C114" s="17" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A104" s="21" t="s">
+    <row r="115" spans="1:3" ht="34" x14ac:dyDescent="0.45">
+      <c r="A115" s="27" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A106" s="23" t="s">
+      <c r="B115" s="18" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A108" s="22" t="s">
+      <c r="C115" s="18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A110" s="21" t="s">
+    <row r="116" spans="1:3" ht="51" x14ac:dyDescent="0.45">
+      <c r="A116" s="27" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A112" s="24" t="s">
+      <c r="B116" s="18" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A114" s="27" t="s">
+      <c r="C116" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B114" s="18" t="s">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A118" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A120" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="C114" s="18" t="s">
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A121" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="34" x14ac:dyDescent="0.45">
-      <c r="A115" s="28" t="s">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A122" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B115" s="19" t="s">
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A123" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="C115" s="19" t="s">
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A124" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="51" x14ac:dyDescent="0.45">
-      <c r="A116" s="28" t="s">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A126" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="B116" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C116" s="19" t="s">
+    </row>
+    <row r="128" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+      <c r="A128" s="23" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A129" s="30" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A118" s="21" t="s">
+      <c r="B129" s="28" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A130" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B130" s="29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+      <c r="A131" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B131" s="29" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A132" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B132" s="29" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A120" s="24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A121" s="21" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A122" s="21" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A123" s="21" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A124" s="21" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A126" s="23" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A128" s="24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" s="31" t="s">
+    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+      <c r="A133" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="B129" s="29" t="s">
+      <c r="B133" s="29" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A130" s="32" t="s">
+    <row r="134" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A134" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B130" s="30" t="s">
+      <c r="B134" s="29" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.45">
-      <c r="A131" s="32" t="s">
+    <row r="135" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A135" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="B131" s="30" t="s">
+      <c r="B135" s="29" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A132" s="32" t="s">
+    <row r="136" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="A136" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="B132" s="30" t="s">
+      <c r="B136" s="29" t="s">
         <v>165</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.45">
-      <c r="A133" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="B133" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A134" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="B134" s="30" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A135" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="B135" s="30" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A136" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="B136" s="30" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -10706,182 +11528,199 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CBC90B-AC39-46A5-A2E0-8D721E775682}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.9140625" style="34" customWidth="1"/>
-    <col min="2" max="2" width="21.58203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22" style="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.25" style="34" customWidth="1"/>
+    <col min="1" max="1" width="25.9140625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="21.58203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.58203125" style="32" customWidth="1"/>
+    <col min="4" max="4" width="49.08203125" style="32" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="85" x14ac:dyDescent="0.45">
+      <c r="A2" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="35">
+        <v>46274</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="86" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="35">
+        <v>46274</v>
+      </c>
+      <c r="D3" s="33"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="33" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="86" t="s">
+        <v>318</v>
+      </c>
+      <c r="C4" s="35">
+        <v>46274</v>
+      </c>
+      <c r="D4" s="33"/>
+    </row>
+    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A5" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B5" s="33"/>
+      <c r="C5" s="35">
+        <v>46275</v>
+      </c>
+      <c r="D5" s="33"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B6" s="33"/>
+      <c r="C6" s="35">
+        <v>46275</v>
+      </c>
+      <c r="D6" s="33"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="B7" s="33"/>
+      <c r="C7" s="35">
+        <v>46276</v>
+      </c>
+      <c r="D7" s="33"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="D1" s="33" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="35">
+        <v>46276</v>
+      </c>
+      <c r="D8" s="33"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="33" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="35" t="s">
+      <c r="B9" s="33"/>
+      <c r="C9" s="35">
+        <v>46276</v>
+      </c>
+      <c r="D9" s="33"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="37">
-        <v>46274</v>
-      </c>
-      <c r="D2" s="35"/>
-    </row>
-    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A3" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="37">
-        <v>46274</v>
-      </c>
-      <c r="D3" s="35"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="37">
-        <v>46274</v>
-      </c>
-      <c r="D4" s="35"/>
-    </row>
-    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A5" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="37">
-        <v>46275</v>
-      </c>
-      <c r="D5" s="35"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="37">
-        <v>46275</v>
-      </c>
-      <c r="D6" s="35"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="37">
-        <v>46276</v>
-      </c>
-      <c r="D7" s="35"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="37">
-        <v>46276</v>
-      </c>
-      <c r="D8" s="35"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="37">
-        <v>46276</v>
-      </c>
-      <c r="D9" s="35"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="37">
-        <v>46279</v>
-      </c>
-      <c r="D10" s="35"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="85">
+        <v>46279.645833333336</v>
+      </c>
+      <c r="D10" s="33"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B3" location="'1. 문제 정의(가설 트리)'!A1" display="링크" xr:uid="{9B58827D-A9B6-4981-86A2-3CC3DF8472F8}"/>
+    <hyperlink ref="B4" location="'2. 지표 지도 그리기'!A1" display="링크" xr:uid="{5F5F2A00-658D-459F-A336-5D9C21F7F45B}"/>
+    <hyperlink ref="B2" location="Dictionary!A1" display="Starbucks Rewards App" xr:uid="{9C53DA75-F66E-47CA-93FD-9BD68A60C51A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD923F7-2D04-4478-AC72-2447676D9924}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="3" width="16.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.6640625" style="1"/>
+    <col min="5" max="5" width="9.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="44.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="38.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.6640625" style="1" customWidth="1"/>
     <col min="8" max="9" width="8.6640625" style="1"/>
     <col min="10" max="10" width="6.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="7" t="s">
+      <c r="A1" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>27</v>
+      <c r="F1" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="45" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="11"/>
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
       <c r="A3" s="39"/>
@@ -10889,31 +11728,31 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G3" s="12"/>
+        <v>39</v>
+      </c>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="39"/>
       <c r="B4" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="3"/>
-      <c r="G4" s="12"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="39"/>
@@ -10921,14 +11760,14 @@
         <v>2</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="3"/>
-      <c r="G5" s="12"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
       <c r="A6" s="39"/>
@@ -10936,187 +11775,197 @@
         <v>3</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="40"/>
-      <c r="B7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="16"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="41" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C7" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="11"/>
+      <c r="C8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="42"/>
+      <c r="A9" s="47"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="12"/>
+      <c r="G9" s="10" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="42"/>
+      <c r="A10" s="47"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>25</v>
+        <v>230</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="12"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="42"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="47"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="3"/>
-      <c r="G11" s="12"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="43"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="48"/>
+      <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="16"/>
+      <c r="C12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="10" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A14" s="45"/>
+      <c r="C13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="42"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="12"/>
+        <v>40</v>
+      </c>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="45"/>
+      <c r="A15" s="42"/>
       <c r="B15" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="12" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="43"/>
+      <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="46"/>
-      <c r="B16" s="17" t="s">
+      <c r="C16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16" t="s">
-        <v>38</v>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="52" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -11132,28 +11981,207 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13FF030F-F06A-41B1-B87E-BFF5ED98AB05}">
-  <dimension ref="A1:B2"/>
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="48.25" customWidth="1"/>
+    <col min="4" max="4" width="62.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="50"/>
+      <c r="B1" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A2" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="48" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="64" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
+      <c r="D2" s="37" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="A3" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="B2" s="49" t="s">
-        <v>192</v>
-      </c>
+      <c r="D3" s="37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="51"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="51"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="51"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" s="51"/>
+      <c r="B22" s="51"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="51"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" s="51"/>
+      <c r="B23" s="51"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" s="51"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" s="51"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="51"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" s="51"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" s="51"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" s="51"/>
+      <c r="B28" s="51"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11164,22 +12192,613 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B68908F-2BBD-42FC-9E49-502A762C6F8E}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E75"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="32.58203125" style="57" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="57" customWidth="1"/>
+    <col min="3" max="3" width="57.9140625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="16.08203125" style="57" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" style="57" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="57"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="49" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="B1" s="49" t="s">
         <v>197</v>
       </c>
+      <c r="C1" s="49" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="D2" s="70" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="A3" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="59" t="s">
+        <v>289</v>
+      </c>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+    </row>
+    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A6" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>207</v>
+      </c>
+      <c r="C6" s="62" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A7" s="83"/>
+      <c r="B7" s="61" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="62" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A8" s="83"/>
+      <c r="B8" s="61" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="62" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="83"/>
+      <c r="B9" s="61" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="62" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="84"/>
+      <c r="B10" s="61" t="s">
+        <v>314</v>
+      </c>
+      <c r="C10" s="62" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="81" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C12" s="63"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="72" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
+    </row>
+    <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="64" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="65"/>
+      <c r="C14" s="66"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="59" t="s">
+        <v>291</v>
+      </c>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="67" t="s">
+        <v>211</v>
+      </c>
+      <c r="B32" s="68"/>
+      <c r="C32" s="69"/>
+    </row>
+    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="60" t="s">
+        <v>237</v>
+      </c>
+      <c r="B33" s="70" t="s">
+        <v>212</v>
+      </c>
+      <c r="C33" s="71" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="60"/>
+      <c r="B34" s="70" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="71"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="60"/>
+      <c r="B35" s="70" t="s">
+        <v>214</v>
+      </c>
+      <c r="C35" s="71"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="60"/>
+      <c r="B36" s="70" t="s">
+        <v>215</v>
+      </c>
+      <c r="C36" s="71"/>
+    </row>
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A37" s="60"/>
+      <c r="B37" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="C37" s="71"/>
+    </row>
+    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="71" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="60"/>
+      <c r="B39" s="70" t="s">
+        <v>219</v>
+      </c>
+      <c r="C39" s="71"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="60"/>
+      <c r="B40" s="70" t="s">
+        <v>220</v>
+      </c>
+      <c r="C40" s="71"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="72" t="s">
+        <v>288</v>
+      </c>
+      <c r="B42" s="73"/>
+      <c r="C42" s="74"/>
+    </row>
+    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="60" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+    </row>
+    <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="60" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="59" t="s">
+        <v>287</v>
+      </c>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="B47" s="55" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" s="55" t="s">
+        <v>249</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>250</v>
+      </c>
+      <c r="E47" s="55" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A48" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="B48" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A49" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="B49" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="C49" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A50" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="B50" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="C50" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A51" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="B51" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A52" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="B52" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C52" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A53" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="B53" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C53" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="B54" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C54" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="D54" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A55" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B55" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="D55" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E55" s="53" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A56" s="53"/>
+      <c r="B56" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="D56" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="E56" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A57" s="53"/>
+      <c r="B57" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="E57" s="75" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="77" t="s">
+        <v>292</v>
+      </c>
+      <c r="B59" s="78"/>
+      <c r="C59" s="79"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" s="80" t="s">
+        <v>293</v>
+      </c>
+      <c r="B60" s="80" t="s">
+        <v>294</v>
+      </c>
+      <c r="C60" s="80" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A61" s="76" t="s">
+        <v>296</v>
+      </c>
+      <c r="B61" s="76" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" s="76" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A62" s="76" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="76" t="s">
+        <v>300</v>
+      </c>
+      <c r="C62" s="76" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A63" s="76" t="s">
+        <v>302</v>
+      </c>
+      <c r="B63" s="76" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="76" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" s="76" t="s">
+        <v>305</v>
+      </c>
+      <c r="B64" s="76" t="s">
+        <v>306</v>
+      </c>
+      <c r="C64" s="76" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="59" t="s">
+        <v>308</v>
+      </c>
+      <c r="B66" s="59"/>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="56" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
+      <c r="D68" s="56"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="56" t="s">
+        <v>279</v>
+      </c>
+      <c r="B69" s="56"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="56"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="56" t="s">
+        <v>280</v>
+      </c>
+      <c r="B70" s="56"/>
+      <c r="C70" s="56"/>
+      <c r="D70" s="56"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="56" t="s">
+        <v>281</v>
+      </c>
+      <c r="B71" s="56"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="56"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="56" t="s">
+        <v>282</v>
+      </c>
+      <c r="B72" s="56"/>
+      <c r="C72" s="56"/>
+      <c r="D72" s="56"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="56" t="s">
+        <v>283</v>
+      </c>
+      <c r="B73" s="56"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="56"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="56" t="s">
+        <v>284</v>
+      </c>
+      <c r="B74" s="56"/>
+      <c r="C74" s="56"/>
+      <c r="D74" s="56"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="56" t="s">
+        <v>285</v>
+      </c>
+      <c r="B75" s="56"/>
+      <c r="C75" s="56"/>
+      <c r="D75" s="56"/>
     </row>
   </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="C33:C37"/>
+    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A6:A10"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/project_2/project2_project status(C2)xlsx.xlsx
+++ b/project_2/project2_project status(C2)xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B5C75D-AF26-46AF-BC40-CEF79F2B3CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D23758-A6CB-413A-823C-DAB0C3030AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>H1·H2·H3가 신규·유지·객단가로 매출의 세 축을 빠짐없이 덮는다.</t>
-  </si>
-  <si>
-    <t>가설 트리의 각 가지를 AARRR 어느 단계 지표로 측정할지 매핑한다. HEART, GAME 등 다른 지표 설계 프레임워크를 적용할 수 있다.</t>
   </si>
   <si>
     <r>
@@ -1444,6 +1441,10 @@
     <t>링크</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>가설 트리의 각 가지를 AARRR 어느 단계 지표로 측정할지 매핑한다. HEART, GAME 등 다른 지표 설계 프레임워크를 적용할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1451,7 +1452,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="184" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
+    <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1938,7 +1939,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2053,6 +2054,63 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2060,6 +2118,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2071,65 +2138,41 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2140,35 +2183,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2178,27 +2194,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="184" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -10901,8 +10896,8 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:C136"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C135"/>
+  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="32.9140625" customWidth="1"/>
@@ -10919,597 +10914,626 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A8" s="21" t="s">
+    <row r="6" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="21" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="20" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="17" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="25" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="25" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="20" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="34" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" s="20" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" s="20" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" s="22" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A15" s="23" t="s">
+    <row r="35" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+      <c r="A35" s="20" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+      <c r="A36" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+      <c r="A37" s="20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+      <c r="A39" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="21" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="20" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A16" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A18" s="25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" s="25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A20" s="25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" s="25" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A22" s="25" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" s="25" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" s="25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A25" s="25" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A26" s="25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A27" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A28" s="25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A30" s="22" t="s">
+    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="26"/>
+      <c r="B50" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="25" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="25" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="75" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A31" s="20" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" s="20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A36" s="21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" s="20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" s="22" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" s="20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" s="22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A43" s="21" t="s">
+    <row r="76" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A80" s="23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A81" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A82" s="22" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A83" s="22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A84" s="20" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="86" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A44" s="20" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" s="20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" s="20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" s="22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A50" s="23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A51" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="26"/>
-      <c r="B52" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52" s="17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B54" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" s="18" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="B56" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C57" s="18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="25" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="25" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A65" s="25" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A66" s="25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A67" s="25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A68" s="25" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" s="25" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A70" s="25" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A71" s="25" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A72" s="25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A73" s="25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A74" s="25" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A75" s="25" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A77" s="22" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A78" s="20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A79" s="20" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A80" s="20" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A82" s="23" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A83" s="22" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A84" s="22" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A85" s="22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A86" s="20" t="s">
+    <row r="87" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A88" s="21" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A89" s="20" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A90" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A91" s="20" t="s">
+    <row r="90" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="91" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="22" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A93" s="22" t="s">
+    <row r="92" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="93" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A95" s="21" t="s">
+    <row r="94" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A96" s="20" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A97" s="20" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A98" s="20" t="s">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="22" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A100" s="22" t="s">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="100" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="102" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A102" s="21" t="s">
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A101" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A103" s="20" t="s">
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A102" s="20" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A104" s="20" t="s">
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A104" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A106" s="22" t="s">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="106" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A106" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="26" x14ac:dyDescent="0.45">
-      <c r="A108" s="21" t="s">
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A108" s="20" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A110" s="20" t="s">
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="110" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A110" s="23" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="21" x14ac:dyDescent="0.45">
-      <c r="A112" s="23" t="s">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A112" s="26" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A114" s="26" t="s">
+      <c r="B112" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="C112" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C114" s="17" t="s">
+    </row>
+    <row r="113" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A113" s="27" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" ht="34" x14ac:dyDescent="0.45">
-      <c r="A115" s="27" t="s">
+      <c r="B113" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="C113" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="C115" s="18" t="s">
+    </row>
+    <row r="114" spans="1:3" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A114" s="27" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" ht="51" x14ac:dyDescent="0.45">
-      <c r="A116" s="27" t="s">
+      <c r="B114" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="C114" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C116" s="18" t="s">
+    </row>
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A116" s="20" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="118" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A118" s="23" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A118" s="20" t="s">
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A119" s="20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A120" s="20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A121" s="20" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A122" s="20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A124" s="22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:3" ht="21" collapsed="1" x14ac:dyDescent="0.45">
+      <c r="A126" s="23" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A127" s="30" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A120" s="23" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A121" s="20" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A122" s="20" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A123" s="20" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A124" s="20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A126" s="22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="21" x14ac:dyDescent="0.45">
-      <c r="A128" s="23" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A129" s="30" t="s">
+      <c r="B127" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="B129" s="28" t="s">
+    </row>
+    <row r="128" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A128" s="31" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="B128" s="29" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+      <c r="A129" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="B129" s="29" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A130" s="31" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B130" s="29" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A131" s="31" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B131" s="29" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A132" s="31" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B132" s="29" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" ht="51" x14ac:dyDescent="0.45">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A133" s="31" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B133" s="29" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A134" s="31" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B134" s="29" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A135" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="B135" s="29" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="A136" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="B136" s="29" t="s">
-        <v>165</v>
-      </c>
-    </row>
+    </row>
+    <row r="135" spans="1:2" collapsed="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11541,39 +11565,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="C1" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="D1" s="38" t="s">
         <v>170</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="85" x14ac:dyDescent="0.45">
       <c r="A2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="86" t="s">
-        <v>172</v>
+      <c r="B2" s="56" t="s">
+        <v>171</v>
       </c>
       <c r="C2" s="35">
         <v>46274</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A3" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="86" t="s">
-        <v>318</v>
+        <v>174</v>
+      </c>
+      <c r="B3" s="56" t="s">
+        <v>317</v>
       </c>
       <c r="C3" s="35">
         <v>46274</v>
@@ -11582,10 +11606,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="86" t="s">
-        <v>318</v>
+        <v>172</v>
+      </c>
+      <c r="B4" s="56" t="s">
+        <v>317</v>
       </c>
       <c r="C4" s="35">
         <v>46274</v>
@@ -11594,7 +11618,7 @@
     </row>
     <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B5" s="33"/>
       <c r="C5" s="35">
@@ -11604,7 +11628,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B6" s="33"/>
       <c r="C6" s="35">
@@ -11614,7 +11638,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="35">
@@ -11624,7 +11648,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B8" s="33"/>
       <c r="C8" s="35">
@@ -11634,7 +11658,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="35">
@@ -11644,10 +11668,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B10" s="33"/>
-      <c r="C10" s="85">
+      <c r="C10" s="55">
         <v>46279.645833333336</v>
       </c>
       <c r="D10" s="33"/>
@@ -11683,30 +11707,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="G1" s="39" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="57" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -11723,7 +11747,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="39"/>
+      <c r="A3" s="58"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -11740,9 +11764,9 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="39"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>29</v>
@@ -11755,7 +11779,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="39"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -11770,7 +11794,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="39"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -11789,7 +11813,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="40"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -11800,13 +11824,13 @@
         <v>14</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="46" t="s">
+      <c r="A8" s="60" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -11823,11 +11847,11 @@
         <v>36</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="47"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -11840,11 +11864,11 @@
       <c r="E9" s="5"/>
       <c r="F9" s="3"/>
       <c r="G9" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="47"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -11855,13 +11879,13 @@
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="47"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -11876,7 +11900,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="48"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -11889,11 +11913,11 @@
       <c r="E12" s="13"/>
       <c r="F12" s="14"/>
       <c r="G12" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="63" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -11906,15 +11930,15 @@
         <v>14</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="42"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -11931,9 +11955,9 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="42"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -11942,17 +11966,17 @@
         <v>13</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="43"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -11964,8 +11988,8 @@
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="52" t="s">
-        <v>225</v>
+      <c r="G16" s="42" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -11984,7 +12008,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -11994,194 +12018,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="50"/>
-      <c r="B1" s="49" t="s">
+      <c r="A1" s="41"/>
+      <c r="B1" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="D1" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="D1" s="49" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A2" s="40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="A3" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="37" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A2" s="49" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="C3" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="51"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="51"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A12" s="51"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="51"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="51"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="51"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="51"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A16" s="51"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="51"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="51"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="51"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="51"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A21" s="51"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="51"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A22" s="51"/>
-      <c r="B22" s="51"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="51"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A23" s="51"/>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A24" s="51"/>
-      <c r="B24" s="51"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="51"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A25" s="51"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="51"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A26" s="51"/>
-      <c r="B26" s="51"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="51"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A27" s="51"/>
-      <c r="B27" s="51"/>
-      <c r="C27" s="51"/>
-      <c r="D27" s="51"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A28" s="51"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12198,575 +12072,575 @@
   <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="32.58203125" style="57" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="57" customWidth="1"/>
-    <col min="3" max="3" width="57.9140625" style="57" customWidth="1"/>
-    <col min="4" max="4" width="16.08203125" style="57" customWidth="1"/>
-    <col min="5" max="5" width="17.08203125" style="57" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="57"/>
+    <col min="1" max="1" width="32.58203125" style="45" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="45" customWidth="1"/>
+    <col min="3" max="3" width="57.9140625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="16.08203125" style="45" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" style="45" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="C1" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>316</v>
+      <c r="D1" s="40" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="36" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="D2" s="70" t="s">
-        <v>317</v>
+        <v>234</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="B3" s="58" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+    </row>
+    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A6" s="75" t="s">
+        <v>205</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A7" s="76"/>
+      <c r="B7" s="47" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" s="48" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="59" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A8" s="76"/>
+      <c r="B8" s="47" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="76"/>
+      <c r="B9" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="77"/>
+      <c r="B10" s="47" t="s">
+        <v>313</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="54" t="s">
+        <v>309</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C12" s="49"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="67" t="s">
         <v>289</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-    </row>
-    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="B6" s="61" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" s="62" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="83"/>
-      <c r="B7" s="61" t="s">
-        <v>309</v>
-      </c>
-      <c r="C7" s="62" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="83"/>
-      <c r="B8" s="61" t="s">
-        <v>312</v>
-      </c>
-      <c r="C8" s="62" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="83"/>
-      <c r="B9" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" s="62" t="s">
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
+    </row>
+    <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="79"/>
+      <c r="C14" s="80"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="73" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="71"/>
+      <c r="C32" s="72"/>
+    </row>
+    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="74" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="66"/>
+      <c r="B34" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="74"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="66"/>
+      <c r="B35" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="74"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="66"/>
+      <c r="B36" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="74"/>
+    </row>
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A37" s="66"/>
+      <c r="B37" s="48" t="s">
+        <v>216</v>
+      </c>
+      <c r="C37" s="74"/>
+    </row>
+    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="50" t="s">
+        <v>217</v>
+      </c>
+      <c r="C38" s="74" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="66"/>
+      <c r="B39" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="74"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="66"/>
+      <c r="B40" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C40" s="74"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="67" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" s="68"/>
+      <c r="C42" s="69"/>
+    </row>
+    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+    </row>
+    <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="73" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="84"/>
-      <c r="B10" s="61" t="s">
-        <v>314</v>
-      </c>
-      <c r="C10" s="62" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="81" t="s">
-        <v>310</v>
-      </c>
-      <c r="B11" s="61" t="s">
-        <v>209</v>
-      </c>
-      <c r="C11" s="62" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="C12" s="63"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
-    </row>
-    <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="64" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="59" t="s">
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="73"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B47" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="44" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A48" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>252</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A49" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="D49" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A50" s="43" t="s">
+        <v>255</v>
+      </c>
+      <c r="B50" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A51" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="E51" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A52" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="D52" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="E52" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A53" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="B53" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="43" t="s">
+        <v>263</v>
+      </c>
+      <c r="D53" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="B54" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A55" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="B55" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C55" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="E55" s="43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A56" s="43"/>
+      <c r="B56" s="43" t="s">
+        <v>269</v>
+      </c>
+      <c r="C56" s="43" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A57" s="43"/>
+      <c r="B57" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="C57" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>274</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="67" t="s">
-        <v>211</v>
-      </c>
-      <c r="B32" s="68"/>
-      <c r="C32" s="69"/>
-    </row>
-    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="B33" s="70" t="s">
-        <v>212</v>
-      </c>
-      <c r="C33" s="71" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="60"/>
-      <c r="B34" s="70" t="s">
-        <v>213</v>
-      </c>
-      <c r="C34" s="71"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="60"/>
-      <c r="B35" s="70" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" s="71"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="60"/>
-      <c r="B36" s="70" t="s">
-        <v>215</v>
-      </c>
-      <c r="C36" s="71"/>
-    </row>
-    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="60"/>
-      <c r="B37" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="C37" s="71"/>
-    </row>
-    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="60" t="s">
-        <v>238</v>
-      </c>
-      <c r="B38" s="70" t="s">
-        <v>218</v>
-      </c>
-      <c r="C38" s="71" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="60"/>
-      <c r="B39" s="70" t="s">
-        <v>219</v>
-      </c>
-      <c r="C39" s="71"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="60"/>
-      <c r="B40" s="70" t="s">
-        <v>220</v>
-      </c>
-      <c r="C40" s="71"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="72" t="s">
-        <v>288</v>
-      </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="74"/>
-    </row>
-    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="60" t="s">
-        <v>222</v>
-      </c>
-      <c r="B43" s="60"/>
-      <c r="C43" s="60"/>
-    </row>
-    <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="60" t="s">
-        <v>223</v>
-      </c>
-      <c r="B44" s="60"/>
-      <c r="C44" s="60"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="59" t="s">
-        <v>287</v>
-      </c>
-      <c r="B46" s="59"/>
-      <c r="C46" s="59"/>
-      <c r="D46" s="59"/>
-      <c r="E46" s="59"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A47" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="B47" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="C47" s="55" t="s">
-        <v>249</v>
-      </c>
-      <c r="D47" s="55" t="s">
-        <v>250</v>
-      </c>
-      <c r="E47" s="55" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A48" s="53" t="s">
-        <v>252</v>
-      </c>
-      <c r="B48" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="C48" s="53" t="s">
-        <v>253</v>
-      </c>
-      <c r="D48" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="E48" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A49" s="53" t="s">
-        <v>254</v>
-      </c>
-      <c r="B49" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="C49" s="53" t="s">
-        <v>255</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A50" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="B50" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="C50" s="53" t="s">
-        <v>257</v>
-      </c>
-      <c r="D50" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="E50" s="53" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A51" s="53" t="s">
-        <v>259</v>
-      </c>
-      <c r="B51" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="C51" s="53" t="s">
-        <v>260</v>
-      </c>
-      <c r="D51" s="53" t="s">
-        <v>246</v>
-      </c>
-      <c r="E51" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A52" s="53" t="s">
-        <v>261</v>
-      </c>
-      <c r="B52" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="C52" s="53" t="s">
-        <v>262</v>
-      </c>
-      <c r="D52" s="53" t="s">
-        <v>246</v>
-      </c>
-      <c r="E52" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A53" s="53" t="s">
-        <v>263</v>
-      </c>
-      <c r="B53" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="C53" s="53" t="s">
-        <v>264</v>
-      </c>
-      <c r="D53" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="E53" s="53" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A54" s="53" t="s">
-        <v>265</v>
-      </c>
-      <c r="B54" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="C54" s="53" t="s">
-        <v>266</v>
-      </c>
-      <c r="D54" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="E54" s="53" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A55" s="53" t="s">
-        <v>267</v>
-      </c>
-      <c r="B55" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="C55" s="53" t="s">
-        <v>268</v>
-      </c>
-      <c r="D55" s="53" t="s">
-        <v>247</v>
-      </c>
-      <c r="E55" s="53" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A56" s="53"/>
-      <c r="B56" s="54" t="s">
-        <v>270</v>
-      </c>
-      <c r="C56" s="54" t="s">
-        <v>272</v>
-      </c>
-      <c r="D56" s="54" t="s">
-        <v>273</v>
-      </c>
-      <c r="E56" s="75" t="s">
+      <c r="B59" s="83"/>
+      <c r="C59" s="84"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" s="53" t="s">
+        <v>292</v>
+      </c>
+      <c r="B60" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="C60" s="53" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A61" s="52" t="s">
+        <v>295</v>
+      </c>
+      <c r="B61" s="52" t="s">
+        <v>296</v>
+      </c>
+      <c r="C61" s="52" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A62" s="52" t="s">
+        <v>298</v>
+      </c>
+      <c r="B62" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="C62" s="52" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A63" s="52" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="73" t="s">
+        <v>307</v>
+      </c>
+      <c r="B66" s="73"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="73"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="81" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
-      <c r="A57" s="53"/>
-      <c r="B57" s="54" t="s">
-        <v>271</v>
-      </c>
-      <c r="C57" s="54" t="s">
-        <v>274</v>
-      </c>
-      <c r="D57" s="54" t="s">
-        <v>275</v>
-      </c>
-      <c r="E57" s="75" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="77" t="s">
-        <v>292</v>
-      </c>
-      <c r="B59" s="78"/>
-      <c r="C59" s="79"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A60" s="80" t="s">
-        <v>293</v>
-      </c>
-      <c r="B60" s="80" t="s">
-        <v>294</v>
-      </c>
-      <c r="C60" s="80" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A61" s="76" t="s">
-        <v>296</v>
-      </c>
-      <c r="B61" s="76" t="s">
-        <v>297</v>
-      </c>
-      <c r="C61" s="76" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A62" s="76" t="s">
-        <v>299</v>
-      </c>
-      <c r="B62" s="76" t="s">
-        <v>300</v>
-      </c>
-      <c r="C62" s="76" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A63" s="76" t="s">
-        <v>302</v>
-      </c>
-      <c r="B63" s="76" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="76" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A64" s="76" t="s">
-        <v>305</v>
-      </c>
-      <c r="B64" s="76" t="s">
-        <v>306</v>
-      </c>
-      <c r="C64" s="76" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="59" t="s">
-        <v>308</v>
-      </c>
-      <c r="B66" s="59"/>
-      <c r="C66" s="59"/>
-      <c r="D66" s="59"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="56" t="s">
+      <c r="B67" s="81"/>
+      <c r="C67" s="81"/>
+      <c r="D67" s="81"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="B67" s="56"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="56"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="56" t="s">
+      <c r="B68" s="81"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="81" t="s">
         <v>278</v>
       </c>
-      <c r="B68" s="56"/>
-      <c r="C68" s="56"/>
-      <c r="D68" s="56"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="56" t="s">
+      <c r="B69" s="81"/>
+      <c r="C69" s="81"/>
+      <c r="D69" s="81"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="B69" s="56"/>
-      <c r="C69" s="56"/>
-      <c r="D69" s="56"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="56" t="s">
+      <c r="B70" s="81"/>
+      <c r="C70" s="81"/>
+      <c r="D70" s="81"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="81" t="s">
         <v>280</v>
       </c>
-      <c r="B70" s="56"/>
-      <c r="C70" s="56"/>
-      <c r="D70" s="56"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="56" t="s">
+      <c r="B71" s="81"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="81"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="81" t="s">
         <v>281</v>
       </c>
-      <c r="B71" s="56"/>
-      <c r="C71" s="56"/>
-      <c r="D71" s="56"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="56" t="s">
+      <c r="B72" s="81"/>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="81" t="s">
         <v>282</v>
       </c>
-      <c r="B72" s="56"/>
-      <c r="C72" s="56"/>
-      <c r="D72" s="56"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="56" t="s">
+      <c r="B73" s="81"/>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="81" t="s">
         <v>283</v>
       </c>
-      <c r="B73" s="56"/>
-      <c r="C73" s="56"/>
-      <c r="D73" s="56"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="56" t="s">
+      <c r="B74" s="81"/>
+      <c r="C74" s="81"/>
+      <c r="D74" s="81"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="81" t="s">
         <v>284</v>
       </c>
-      <c r="B74" s="56"/>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="56" t="s">
-        <v>285</v>
-      </c>
-      <c r="B75" s="56"/>
-      <c r="C75" s="56"/>
-      <c r="D75" s="56"/>
+      <c r="B75" s="81"/>
+      <c r="C75" s="81"/>
+      <c r="D75" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -12782,11 +12656,6 @@
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A71:D71"/>
     <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -12795,6 +12664,11 @@
     <mergeCell ref="A33:A37"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A43:C43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
